--- a/data/merged/2026-10-08/MERGED_FR_Spot-Cleaner_2026-10-08.xlsx
+++ b/data/merged/2026-10-08/MERGED_FR_Spot-Cleaner_2026-10-08.xlsx
@@ -6958,94 +6958,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId48" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="49" name="Product 49">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId49" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Product 50">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId50" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7387,7 +7299,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR49"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -14762,163 +14674,163 @@
       <c r="B33" s="13"/>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>B07999DC2C</t>
+          <t>B0C3VKT151</t>
         </is>
       </c>
       <c r="D33" s="14"/>
       <c r="E33" s="14"/>
       <c r="F33" s="14" t="inlineStr">
         <is>
-          <t>Bissell</t>
+          <t>SUPER CLEAN</t>
         </is>
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/BISSELL/page/257B1210-BA3F-4555-82AC-76498F62C992?lp_asin=B07999DC2C&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.fr/SUPER-CLEAN/b/ref=bl_dp_s_web_56519001031?ie=UTF8&amp;node=56519001031&amp;field-lbr_brands_browse-bin=SUPER+CLEAN</t>
         </is>
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>Bissell Brosse pour Taches Tenaces, Noir, 15 cm</t>
+          <t>SUPER CLEAN Nettoyant tissus d'ameublement et tapis, 2 x 500 mlsConcentré économique contre les taches et les odeurs pour c</t>
         </is>
       </c>
       <c r="I33" s="14"/>
       <c r="J33" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B07999DC2C?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0C3VKT151?psc=1</t>
         </is>
       </c>
       <c r="K33" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41iS9PbnYAL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/51BtUWuNe6L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L33" s="14" t="inlineStr">
         <is>
-          <t>B07999DC2C</t>
+          <t>B0C3VKT151</t>
         </is>
       </c>
       <c r="M33" s="14" t="inlineStr">
         <is>
-          <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Accessoires pour nettoyeurs tapis et moquettes</t>
+          <t>Cuisine et Maison:Produits et accessoires de nettoyage:Produits d'entretien:Nettoyeurs tapis et moquettes</t>
         </is>
       </c>
       <c r="N33" s="14" t="inlineStr">
         <is>
-          <t>Voir les 100 premiers en Cuisine et Maison</t>
+          <t>Voir les 100 premiers en Epicerie</t>
         </is>
       </c>
       <c r="O33" s="15">
-        <v>3358</v>
+        <v>1865</v>
       </c>
       <c r="P33" s="15">
-        <v>-953</v>
+        <v>-43</v>
       </c>
       <c r="Q33" s="16">
-        <v>-0.4</v>
+        <v>-0.02</v>
       </c>
       <c r="R33" s="17" t="inlineStr">
         <is>
-          <t>Accessoires pour nettoyeurs tapis et moquettes</t>
+          <t>Nettoyants pour tapis de maison
+Produits d’entretien ménagers</t>
         </is>
       </c>
       <c r="S33" s="18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7
+313</t>
         </is>
       </c>
       <c r="T33" s="15">
-        <v>329</v>
+        <v>282</v>
       </c>
       <c r="U33" s="16">
-        <v>-0.33</v>
+        <v>-0.17</v>
       </c>
       <c r="V33" s="15">
-        <v>8222</v>
-      </c>
-      <c r="W33" s="15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X33" s="15">
-        <v>1250</v>
-      </c>
+        <v>7524</v>
+      </c>
+      <c r="W33" s="15"/>
+      <c r="X33" s="15"/>
       <c r="Y33" s="19">
         <v>6</v>
       </c>
       <c r="Z33" s="20">
-        <v>20.82</v>
+        <v>26.68</v>
       </c>
       <c r="AA33"/>
       <c r="AB33"/>
       <c r="AC33" s="15">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="AD33" s="19">
-        <v>1392</v>
+        <v>9047</v>
       </c>
       <c r="AE33" s="15">
-        <v>4</v>
+        <v>1490</v>
       </c>
       <c r="AF33" s="21">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AG33" s="22">
-        <v>0.012199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AH33" s="20">
-        <v>5.15</v>
+        <v>5.96</v>
       </c>
       <c r="AI33" s="16">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="AJ33"/>
       <c r="AK33" s="13" t="inlineStr">
         <is>
-          <t>2018-06-01</t>
+          <t>2023-07-12</t>
         </is>
       </c>
       <c r="AL33" s="19">
-        <v>3051</v>
+        <v>1183</v>
       </c>
       <c r="AM33" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN33" s="13"/>
       <c r="AO33" s="13"/>
       <c r="AP33"/>
       <c r="AQ33" s="19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR33" s="19">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AS33" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Innochem</t>
         </is>
       </c>
       <c r="AT33" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU33" s="13"/>
-      <c r="AV33" s="14"/>
-      <c r="AW33" s="13"/>
-      <c r="AX33" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="AY33" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="AU33" s="13" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="AV33" s="14" t="inlineStr">
+        <is>
+          <t>Teningen 79331 DE</t>
+        </is>
+      </c>
+      <c r="AW33" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3H8GAVD67YD0F</t>
+        </is>
+      </c>
+      <c r="AX33" s="13"/>
+      <c r="AY33" s="13"/>
       <c r="AZ33" s="13"/>
       <c r="BA33" s="13"/>
       <c r="BB33" s="13"/>
@@ -14936,49 +14848,45 @@
       <c r="BF33" s="13"/>
       <c r="BG33" s="13"/>
       <c r="BH33" s="14"/>
-      <c r="BI33" s="23" t="inlineStr">
-        <is>
-          <t>Choix d'Amazon</t>
-        </is>
-      </c>
+      <c r="BI33" s="23"/>
       <c r="BJ33" s="23" t="inlineStr">
         <is>
-          <t>137 g</t>
+          <t>500 g</t>
         </is>
       </c>
       <c r="BK33" s="23" t="inlineStr">
         <is>
-          <t>137.00 g</t>
+          <t>500.00 g</t>
         </is>
       </c>
       <c r="BL33" s="23" t="inlineStr">
         <is>
-          <t>40 x 25 x 15 cm</t>
+          <t>19,5 x 18,1 x 7,3 cm</t>
         </is>
       </c>
       <c r="BM33" s="23" t="inlineStr">
         <is>
-          <t>40.00 x 25.00 x 15.00 cm</t>
+          <t>19.50 x 18.10 x 7.30 cm</t>
         </is>
       </c>
       <c r="BN33" s="23" t="inlineStr">
         <is>
-          <t>150 g</t>
+          <t>1.11 kg</t>
         </is>
       </c>
       <c r="BO33" s="23" t="inlineStr">
         <is>
-          <t>150.00 g</t>
+          <t>1.11 kg</t>
         </is>
       </c>
       <c r="BP33" s="23" t="inlineStr">
         <is>
-          <t>16.5 x 15 x 7.3 cm</t>
+          <t>19.5 x 18.1 x 7.3 cm</t>
         </is>
       </c>
       <c r="BQ33" s="23" t="inlineStr">
         <is>
-          <t>16.50 x 15.00 x 7.30 cm</t>
+          <t>19.50 x 18.10 x 7.30 cm</t>
         </is>
       </c>
       <c r="BR33" s="13" t="inlineStr">
@@ -14994,121 +14902,117 @@
       <c r="B34" s="13"/>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>B0C3VKT151</t>
+          <t>B0H3LCDNGF</t>
         </is>
       </c>
       <c r="D34" s="14"/>
       <c r="E34" s="14"/>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>SUPER CLEAN</t>
+          <t>LEHMANN</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/SUPER-CLEAN/b/ref=bl_dp_s_web_56519001031?ie=UTF8&amp;node=56519001031&amp;field-lbr_brands_browse-bin=SUPER+CLEAN</t>
+          <t>https://www.amazon.fr/stores/LEHMANN/page/EAB8CEA1-93E8-4C19-BC95-67B7BFD404B9?lp_asin=B0H3LCDNGF&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>SUPER CLEAN Nettoyant tissus d'ameublement et tapis, 2 x 500 mlsConcentré économique contre les taches et les odeurs pour c</t>
+          <t>LEHMANN SteamWash 1800 - Nettoyeur Vapeur 4 en 1 &amp; Aspirateur Injecteur Extracteur, Nettoyeur à Main Portable Canapé, Tapis,</t>
         </is>
       </c>
       <c r="I34" s="14"/>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0C3VKT151?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0H3LCDNGF?psc=1</t>
         </is>
       </c>
       <c r="K34" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51BtUWuNe6L._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41Md9nniqDL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>B0C3VKT151</t>
+          <t>B0H3LCDNGF</t>
         </is>
       </c>
       <c r="M34" s="14" t="inlineStr">
         <is>
-          <t>Cuisine et Maison:Produits et accessoires de nettoyage:Produits d'entretien:Nettoyeurs tapis et moquettes</t>
+          <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Nettoyeurs tapis et moquettes</t>
         </is>
       </c>
       <c r="N34" s="14" t="inlineStr">
         <is>
-          <t>Voir les 100 premiers en Epicerie</t>
+          <t>Voir les 100 premiers en Cuisine et Maison</t>
         </is>
       </c>
       <c r="O34" s="15">
-        <v>1865</v>
+        <v>22933</v>
       </c>
       <c r="P34" s="15">
-        <v>-43</v>
+        <v>8813</v>
       </c>
       <c r="Q34" s="16">
-        <v>-0.02</v>
+        <v>0.28</v>
       </c>
       <c r="R34" s="17" t="inlineStr">
         <is>
-          <t>Nettoyants pour tapis de maison
-Produits d’entretien ménagers</t>
+          <t>Nettoyeurs tapis et moquettes</t>
         </is>
       </c>
       <c r="S34" s="18" t="inlineStr">
         <is>
-          <t>7
-313</t>
+          <t>34</t>
         </is>
       </c>
       <c r="T34" s="15">
-        <v>282</v>
+        <v>73</v>
       </c>
       <c r="U34" s="16">
-        <v>-0.17</v>
+        <v>-0.42</v>
       </c>
       <c r="V34" s="15">
-        <v>7524</v>
+        <v>7299</v>
       </c>
       <c r="W34" s="15"/>
       <c r="X34" s="15"/>
       <c r="Y34" s="19">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Z34" s="20">
-        <v>26.68</v>
+        <v>99.99</v>
       </c>
       <c r="AA34"/>
       <c r="AB34"/>
-      <c r="AC34" s="15">
-        <v>26</v>
-      </c>
+      <c r="AC34" s="15"/>
       <c r="AD34" s="19">
-        <v>9047</v>
+        <v>38</v>
       </c>
       <c r="AE34" s="15">
-        <v>1490</v>
+        <v>10</v>
       </c>
       <c r="AF34" s="21">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AG34" s="22">
-        <v>0</v>
+        <v>0.13699999999999998</v>
       </c>
       <c r="AH34" s="20">
-        <v>5.96</v>
+        <v>9.1</v>
       </c>
       <c r="AI34" s="16">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="AJ34"/>
       <c r="AK34" s="13" t="inlineStr">
         <is>
-          <t>2023-07-12</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AL34" s="19">
-        <v>1183</v>
+        <v>128</v>
       </c>
       <c r="AM34" s="13" t="inlineStr">
         <is>
@@ -15119,14 +15023,14 @@
       <c r="AO34" s="13"/>
       <c r="AP34"/>
       <c r="AQ34" s="19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AR34" s="19">
         <v>1</v>
       </c>
       <c r="AS34" s="14" t="inlineStr">
         <is>
-          <t>Innochem</t>
+          <t>Lehmann HG</t>
         </is>
       </c>
       <c r="AT34" s="13" t="inlineStr">
@@ -15136,17 +15040,17 @@
       </c>
       <c r="AU34" s="13" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="AV34" s="14" t="inlineStr">
         <is>
-          <t>Teningen 79331 DE</t>
+          <t>Greater Poland 63-100 PL</t>
         </is>
       </c>
       <c r="AW34" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3H8GAVD67YD0F</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH</t>
         </is>
       </c>
       <c r="AX34" s="13"/>
@@ -15159,11 +15063,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD34" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD34" s="13"/>
       <c r="BE34" s="13"/>
       <c r="BF34" s="13"/>
       <c r="BG34" s="13"/>
@@ -15171,47 +15071,39 @@
       <c r="BI34" s="23"/>
       <c r="BJ34" s="23" t="inlineStr">
         <is>
-          <t>500 g</t>
-        </is>
-      </c>
-      <c r="BK34" s="23" t="inlineStr">
-        <is>
-          <t>500.00 g</t>
-        </is>
-      </c>
+          <t>4,7 Kilogrammes</t>
+        </is>
+      </c>
+      <c r="BK34" s="23"/>
       <c r="BL34" s="23" t="inlineStr">
         <is>
-          <t>19,5 x 18,1 x 7,3 cm</t>
-        </is>
-      </c>
-      <c r="BM34" s="23" t="inlineStr">
-        <is>
-          <t>19.50 x 18.10 x 7.30 cm</t>
-        </is>
-      </c>
+          <t>22P x 32l x 30H centimètres</t>
+        </is>
+      </c>
+      <c r="BM34" s="23"/>
       <c r="BN34" s="23" t="inlineStr">
         <is>
-          <t>1.11 kg</t>
+          <t>5.76 kg</t>
         </is>
       </c>
       <c r="BO34" s="23" t="inlineStr">
         <is>
-          <t>1.11 kg</t>
+          <t>5.76 kg</t>
         </is>
       </c>
       <c r="BP34" s="23" t="inlineStr">
         <is>
-          <t>19.5 x 18.1 x 7.3 cm</t>
+          <t>37.3 x 35.7 x 31.8 cm</t>
         </is>
       </c>
       <c r="BQ34" s="23" t="inlineStr">
         <is>
-          <t>19.50 x 18.10 x 7.30 cm</t>
+          <t>37.30 x 35.70 x 31.80 cm</t>
         </is>
       </c>
       <c r="BR34" s="13" t="inlineStr">
         <is>
-          <t>小包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -15222,40 +15114,40 @@
       <c r="B35" s="13"/>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>B0H3LCDNGF</t>
+          <t>B0GQJ6RWKR</t>
         </is>
       </c>
       <c r="D35" s="14"/>
       <c r="E35" s="14"/>
       <c r="F35" s="14" t="inlineStr">
         <is>
-          <t>LEHMANN</t>
+          <t>Shark</t>
         </is>
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/LEHMANN/page/EAB8CEA1-93E8-4C19-BC95-67B7BFD404B9?lp_asin=B0H3LCDNGF&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.fr/stores/SharkINinja/page/AE46A729-E57D-49FA-B00E-8125E3841DDD?lp_asin=B0GQJ6RWKR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>LEHMANN SteamWash 1800 - Nettoyeur Vapeur 4 en 1 &amp; Aspirateur Injecteur Extracteur, Nettoyeur à Main Portable Canapé, Tapis,</t>
+          <t>Shark StainForce Shampouineuse sans fil, nettoyeur de taches, pour TapissSuceur plat, tuyaux, 2 formules de nettoyage Carpe</t>
         </is>
       </c>
       <c r="I35" s="14"/>
       <c r="J35" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0H3LCDNGF?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GQJ6RWKR?psc=1</t>
         </is>
       </c>
       <c r="K35" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41Md9nniqDL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/410s8YmSZGL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L35" s="14" t="inlineStr">
         <is>
-          <t>B0H3LCDNGF</t>
+          <t>B0GQJ6RWKR</t>
         </is>
       </c>
       <c r="M35" s="14" t="inlineStr">
@@ -15269,13 +15161,13 @@
         </is>
       </c>
       <c r="O35" s="15">
-        <v>22933</v>
+        <v>40949</v>
       </c>
       <c r="P35" s="15">
-        <v>8813</v>
+        <v>-17949</v>
       </c>
       <c r="Q35" s="16">
-        <v>0.28</v>
+        <v>-0.78</v>
       </c>
       <c r="R35" s="17" t="inlineStr">
         <is>
@@ -15284,95 +15176,89 @@
       </c>
       <c r="S35" s="18" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>47</t>
         </is>
       </c>
       <c r="T35" s="15">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="U35" s="16">
-        <v>-0.42</v>
+        <v>-0.2</v>
       </c>
       <c r="V35" s="15">
-        <v>7299</v>
-      </c>
-      <c r="W35" s="15"/>
-      <c r="X35" s="15"/>
+        <v>6554</v>
+      </c>
+      <c r="W35" s="15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="X35" s="15">
+        <v>4750</v>
+      </c>
       <c r="Y35" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z35" s="20">
-        <v>99.99</v>
+        <v>83.32</v>
       </c>
       <c r="AA35"/>
       <c r="AB35"/>
       <c r="AC35" s="15"/>
       <c r="AD35" s="19">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="AE35" s="15">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AF35" s="21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG35" s="22">
-        <v>0.13699999999999998</v>
+        <v>0.0725</v>
       </c>
       <c r="AH35" s="20">
         <v>9.1</v>
       </c>
       <c r="AI35" s="16">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="AJ35"/>
       <c r="AK35" s="13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AL35" s="19">
-        <v>128</v>
+        <v>176</v>
       </c>
       <c r="AM35" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN35" s="13"/>
       <c r="AO35" s="13"/>
       <c r="AP35"/>
       <c r="AQ35" s="19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AR35" s="19">
         <v>1</v>
       </c>
       <c r="AS35" s="14" t="inlineStr">
         <is>
-          <t>Lehmann HG</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT35" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU35" s="13" t="inlineStr">
-        <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="AV35" s="14" t="inlineStr">
-        <is>
-          <t>Greater Poland 63-100 PL</t>
-        </is>
-      </c>
-      <c r="AW35" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU35" s="13"/>
+      <c r="AV35" s="14"/>
+      <c r="AW35" s="13"/>
       <c r="AX35" s="13"/>
       <c r="AY35" s="13"/>
       <c r="AZ35" s="13"/>
@@ -15383,7 +15269,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD35" s="13"/>
+      <c r="BD35" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE35" s="13"/>
       <c r="BF35" s="13"/>
       <c r="BG35" s="13"/>
@@ -15391,34 +15281,34 @@
       <c r="BI35" s="23"/>
       <c r="BJ35" s="23" t="inlineStr">
         <is>
-          <t>4,7 Kilogrammes</t>
+          <t>4,2 Kilogrammes</t>
         </is>
       </c>
       <c r="BK35" s="23"/>
       <c r="BL35" s="23" t="inlineStr">
         <is>
-          <t>22P x 32l x 30H centimètres</t>
+          <t>28P x 29,8l x 28,7H centimètres</t>
         </is>
       </c>
       <c r="BM35" s="23"/>
       <c r="BN35" s="23" t="inlineStr">
         <is>
-          <t>5.76 kg</t>
+          <t>5.15 kg</t>
         </is>
       </c>
       <c r="BO35" s="23" t="inlineStr">
         <is>
-          <t>5.76 kg</t>
+          <t>5.15 kg</t>
         </is>
       </c>
       <c r="BP35" s="23" t="inlineStr">
         <is>
-          <t>37.3 x 35.7 x 31.8 cm</t>
+          <t>38.8 x 35.3 x 31 cm</t>
         </is>
       </c>
       <c r="BQ35" s="23" t="inlineStr">
         <is>
-          <t>37.30 x 35.70 x 31.80 cm</t>
+          <t>38.80 x 35.30 x 31.00 cm</t>
         </is>
       </c>
       <c r="BR35" s="13" t="inlineStr">
@@ -15434,40 +15324,40 @@
       <c r="B36" s="13"/>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>B0GQJ6RWKR</t>
+          <t>B0FS2B5W6P</t>
         </is>
       </c>
       <c r="D36" s="14"/>
       <c r="E36" s="14"/>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>Shark</t>
+          <t>LEHMANN</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/SharkINinja/page/AE46A729-E57D-49FA-B00E-8125E3841DDD?lp_asin=B0GQJ6RWKR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.fr/stores/LEHMANN/page/EAB8CEA1-93E8-4C19-BC95-67B7BFD404B9?lp_asin=B0FS2B5W6P&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>Shark StainForce Shampouineuse sans fil, nettoyeur de taches, pour TapissSuceur plat, tuyaux, 2 formules de nettoyage Carpe</t>
+          <t>LEHMANN EasyWash Shampouineuse Canapé 2 en 1, Nettoyage Puissant pour Taches Résistantes, Doppio Serbatoio, Nettoyeur Canapé,</t>
         </is>
       </c>
       <c r="I36" s="14"/>
       <c r="J36" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GQJ6RWKR?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0FS2B5W6P?psc=1</t>
         </is>
       </c>
       <c r="K36" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/410s8YmSZGL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71LqABaCHVL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>B0GQJ6RWKR</t>
+          <t>B0FS2B5W6P</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
@@ -15481,13 +15371,13 @@
         </is>
       </c>
       <c r="O36" s="15">
-        <v>40949</v>
+        <v>8375</v>
       </c>
       <c r="P36" s="15">
-        <v>-17949</v>
+        <v>56400</v>
       </c>
       <c r="Q36" s="16">
-        <v>-0.78</v>
+        <v>0.87</v>
       </c>
       <c r="R36" s="17" t="inlineStr">
         <is>
@@ -15496,17 +15386,17 @@
       </c>
       <c r="S36" s="18" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>23</t>
         </is>
       </c>
       <c r="T36" s="15">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="U36" s="16">
-        <v>-0.2</v>
+        <v>0.44</v>
       </c>
       <c r="V36" s="15">
-        <v>6554</v>
+        <v>6119</v>
       </c>
       <c r="W36" s="15" t="inlineStr">
         <is>
@@ -15514,47 +15404,47 @@
         </is>
       </c>
       <c r="X36" s="15">
-        <v>4750</v>
+        <v>3822</v>
       </c>
       <c r="Y36" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z36" s="20">
-        <v>83.32</v>
+        <v>59.99</v>
       </c>
       <c r="AA36"/>
       <c r="AB36"/>
       <c r="AC36" s="15"/>
       <c r="AD36" s="19">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="AE36" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF36" s="21">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="AG36" s="22">
-        <v>0.0725</v>
+        <v>0.0392</v>
       </c>
       <c r="AH36" s="20">
-        <v>9.1</v>
+        <v>8.89</v>
       </c>
       <c r="AI36" s="16">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AJ36"/>
       <c r="AK36" s="13" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="AL36" s="19">
-        <v>176</v>
+        <v>319</v>
       </c>
       <c r="AM36" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN36" s="13"/>
@@ -15564,23 +15454,39 @@
         <v>10</v>
       </c>
       <c r="AR36" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS36" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Lehmann HG</t>
         </is>
       </c>
       <c r="AT36" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU36" s="13"/>
-      <c r="AV36" s="14"/>
-      <c r="AW36" s="13"/>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="AU36" s="13" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="AV36" s="14" t="inlineStr">
+        <is>
+          <t>Greater Poland 63-100 PL</t>
+        </is>
+      </c>
+      <c r="AW36" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH</t>
+        </is>
+      </c>
       <c r="AX36" s="13"/>
-      <c r="AY36" s="13"/>
+      <c r="AY36" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ36" s="13"/>
       <c r="BA36" s="13"/>
       <c r="BB36" s="13"/>
@@ -15589,46 +15495,54 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD36" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD36" s="13"/>
       <c r="BE36" s="13"/>
       <c r="BF36" s="13"/>
       <c r="BG36" s="13"/>
       <c r="BH36" s="14"/>
-      <c r="BI36" s="23"/>
+      <c r="BI36" s="23" t="inlineStr">
+        <is>
+          <t>Choix d'Amazon</t>
+        </is>
+      </c>
       <c r="BJ36" s="23" t="inlineStr">
         <is>
-          <t>4,2 Kilogrammes</t>
-        </is>
-      </c>
-      <c r="BK36" s="23"/>
+          <t>4.5 kg</t>
+        </is>
+      </c>
+      <c r="BK36" s="23" t="inlineStr">
+        <is>
+          <t>4.50 kg</t>
+        </is>
+      </c>
       <c r="BL36" s="23" t="inlineStr">
         <is>
-          <t>28P x 29,8l x 28,7H centimètres</t>
-        </is>
-      </c>
-      <c r="BM36" s="23"/>
+          <t>31.5 x 24 x 35.5 cm</t>
+        </is>
+      </c>
+      <c r="BM36" s="23" t="inlineStr">
+        <is>
+          <t>31.50 x 24.00 x 35.50 cm</t>
+        </is>
+      </c>
       <c r="BN36" s="23" t="inlineStr">
         <is>
-          <t>5.15 kg</t>
+          <t>5.66 kg</t>
         </is>
       </c>
       <c r="BO36" s="23" t="inlineStr">
         <is>
-          <t>5.15 kg</t>
+          <t>5.66 kg</t>
         </is>
       </c>
       <c r="BP36" s="23" t="inlineStr">
         <is>
-          <t>38.8 x 35.3 x 31 cm</t>
+          <t>38 x 36.2 x 26.2 cm</t>
         </is>
       </c>
       <c r="BQ36" s="23" t="inlineStr">
         <is>
-          <t>38.80 x 35.30 x 31.00 cm</t>
+          <t>38.00 x 36.20 x 26.20 cm</t>
         </is>
       </c>
       <c r="BR36" s="13" t="inlineStr">
@@ -15644,40 +15558,40 @@
       <c r="B37" s="13"/>
       <c r="C37" s="14" t="inlineStr">
         <is>
-          <t>B0FS2B5W6P</t>
+          <t>B0CVXJ1VHT</t>
         </is>
       </c>
       <c r="D37" s="14"/>
       <c r="E37" s="14"/>
       <c r="F37" s="14" t="inlineStr">
         <is>
-          <t>LEHMANN</t>
+          <t>Bissell</t>
         </is>
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/LEHMANN/page/EAB8CEA1-93E8-4C19-BC95-67B7BFD404B9?lp_asin=B0FS2B5W6P&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.fr/stores/BISSELL/page/257B1210-BA3F-4555-82AC-76498F62C992?lp_asin=B0CVXJ1VHT&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
-          <t>LEHMANN EasyWash Shampouineuse Canapé 2 en 1, Nettoyage Puissant pour Taches Résistantes, Doppio Serbatoio, Nettoyeur Canapé,</t>
+          <t>BISSELL PowerWash Pet, Nettoyeur de Tapis, Shampouineuse Idéal pour les Propriétaires d'Animaux, Appareil de Nettoyage, Netto</t>
         </is>
       </c>
       <c r="I37" s="14"/>
       <c r="J37" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0FS2B5W6P?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0CVXJ1VHT?psc=1</t>
         </is>
       </c>
       <c r="K37" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71LqABaCHVL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/31jphvfzkmL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L37" s="14" t="inlineStr">
         <is>
-          <t>B0FS2B5W6P</t>
+          <t>B0CVXJ1VHT</t>
         </is>
       </c>
       <c r="M37" s="14" t="inlineStr">
@@ -15691,13 +15605,13 @@
         </is>
       </c>
       <c r="O37" s="15">
-        <v>8375</v>
+        <v>59317</v>
       </c>
       <c r="P37" s="15">
-        <v>56400</v>
+        <v>-129996</v>
       </c>
       <c r="Q37" s="16">
-        <v>0.87</v>
+        <v>-1.38</v>
       </c>
       <c r="R37" s="17" t="inlineStr">
         <is>
@@ -15706,65 +15620,59 @@
       </c>
       <c r="S37" s="18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>50</t>
         </is>
       </c>
       <c r="T37" s="15">
-        <v>102</v>
+        <v>29</v>
       </c>
       <c r="U37" s="16">
-        <v>0.44</v>
+        <v>9</v>
       </c>
       <c r="V37" s="15">
-        <v>6119</v>
-      </c>
-      <c r="W37" s="15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X37" s="15">
-        <v>3822</v>
-      </c>
+        <v>5935</v>
+      </c>
+      <c r="W37" s="15"/>
+      <c r="X37" s="15"/>
       <c r="Y37" s="19">
         <v>1</v>
       </c>
       <c r="Z37" s="20">
-        <v>59.99</v>
+        <v>204.67</v>
       </c>
       <c r="AA37"/>
       <c r="AB37"/>
       <c r="AC37" s="15"/>
       <c r="AD37" s="19">
-        <v>57</v>
+        <v>208</v>
       </c>
       <c r="AE37" s="15">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AF37" s="21">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AG37" s="22">
-        <v>0.0392</v>
+        <v>0</v>
       </c>
       <c r="AH37" s="20">
-        <v>8.89</v>
+        <v>11.24</v>
       </c>
       <c r="AI37" s="16">
-        <v>0.7</v>
+        <v>0.81</v>
       </c>
       <c r="AJ37"/>
       <c r="AK37" s="13" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="AL37" s="19">
-        <v>319</v>
+        <v>960</v>
       </c>
       <c r="AM37" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN37" s="13"/>
@@ -15774,39 +15682,23 @@
         <v>10</v>
       </c>
       <c r="AR37" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS37" s="14" t="inlineStr">
         <is>
-          <t>Lehmann HG</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT37" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU37" s="13" t="inlineStr">
-        <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="AV37" s="14" t="inlineStr">
-        <is>
-          <t>Greater Poland 63-100 PL</t>
-        </is>
-      </c>
-      <c r="AW37" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU37" s="13"/>
+      <c r="AV37" s="14"/>
+      <c r="AW37" s="13"/>
       <c r="AX37" s="13"/>
-      <c r="AY37" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY37" s="13"/>
       <c r="AZ37" s="13"/>
       <c r="BA37" s="13"/>
       <c r="BB37" s="13"/>
@@ -15815,54 +15707,46 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD37" s="13"/>
+      <c r="BD37" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE37" s="13"/>
       <c r="BF37" s="13"/>
       <c r="BG37" s="13"/>
       <c r="BH37" s="14"/>
-      <c r="BI37" s="23" t="inlineStr">
-        <is>
-          <t>Choix d'Amazon</t>
-        </is>
-      </c>
+      <c r="BI37" s="23"/>
       <c r="BJ37" s="23" t="inlineStr">
         <is>
-          <t>4.5 kg</t>
-        </is>
-      </c>
-      <c r="BK37" s="23" t="inlineStr">
-        <is>
-          <t>4.50 kg</t>
-        </is>
-      </c>
+          <t>7,71 Kilogrammes</t>
+        </is>
+      </c>
+      <c r="BK37" s="23"/>
       <c r="BL37" s="23" t="inlineStr">
         <is>
-          <t>31.5 x 24 x 35.5 cm</t>
-        </is>
-      </c>
-      <c r="BM37" s="23" t="inlineStr">
-        <is>
-          <t>31.50 x 24.00 x 35.50 cm</t>
-        </is>
-      </c>
+          <t>42P x 30l x 108H centimètres</t>
+        </is>
+      </c>
+      <c r="BM37" s="23"/>
       <c r="BN37" s="23" t="inlineStr">
         <is>
-          <t>5.66 kg</t>
+          <t>11.05 kg</t>
         </is>
       </c>
       <c r="BO37" s="23" t="inlineStr">
         <is>
-          <t>5.66 kg</t>
+          <t>11.05 kg</t>
         </is>
       </c>
       <c r="BP37" s="23" t="inlineStr">
         <is>
-          <t>38 x 36.2 x 26.2 cm</t>
+          <t>63 x 45 x 32.5 cm</t>
         </is>
       </c>
       <c r="BQ37" s="23" t="inlineStr">
         <is>
-          <t>38.00 x 36.20 x 26.20 cm</t>
+          <t>63.00 x 45.00 x 32.50 cm</t>
         </is>
       </c>
       <c r="BR37" s="13" t="inlineStr">
@@ -15878,40 +15762,40 @@
       <c r="B38" s="13"/>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>B0CVXJ1VHT</t>
+          <t>B01HZUX61M</t>
         </is>
       </c>
       <c r="D38" s="14"/>
       <c r="E38" s="14"/>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>Bissell</t>
+          <t>Tech'N'Fast</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/BISSELL/page/257B1210-BA3F-4555-82AC-76498F62C992?lp_asin=B0CVXJ1VHT&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.fr/stores/Technfast/page/5C561153-C96A-4DCF-BA10-143B211F8707?lp_asin=B01HZUX61M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>BISSELL PowerWash Pet, Nettoyeur de Tapis, Shampouineuse Idéal pour les Propriétaires d'Animaux, Appareil de Nettoyage, Netto</t>
+          <t>Nettoyant textile concentré, canapé, moquette, tapis, sièges auto, détachant, dissout les tâches et neutralise les odeurs - B</t>
         </is>
       </c>
       <c r="I38" s="14"/>
       <c r="J38" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0CVXJ1VHT?psc=1</t>
+          <t>https://www.amazon.fr/dp/B01HZUX61M?psc=1</t>
         </is>
       </c>
       <c r="K38" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31jphvfzkmL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/319Ry9yZeTL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>B0CVXJ1VHT</t>
+          <t>B01HZUX61M</t>
         </is>
       </c>
       <c r="M38" s="14" t="inlineStr">
@@ -15925,13 +15809,13 @@
         </is>
       </c>
       <c r="O38" s="15">
-        <v>59317</v>
+        <v>16042</v>
       </c>
       <c r="P38" s="15">
-        <v>-129996</v>
+        <v>-3040</v>
       </c>
       <c r="Q38" s="16">
-        <v>-1.38</v>
+        <v>-0.21</v>
       </c>
       <c r="R38" s="17" t="inlineStr">
         <is>
@@ -15940,59 +15824,65 @@
       </c>
       <c r="S38" s="18" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="T38" s="15">
-        <v>29</v>
+        <v>183</v>
       </c>
       <c r="U38" s="16">
-        <v>9</v>
+        <v>0.13</v>
       </c>
       <c r="V38" s="15">
-        <v>5935</v>
-      </c>
-      <c r="W38" s="15"/>
-      <c r="X38" s="15"/>
+        <v>5197</v>
+      </c>
+      <c r="W38" s="15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="X38" s="15">
+        <v>3416</v>
+      </c>
       <c r="Y38" s="19">
         <v>1</v>
       </c>
       <c r="Z38" s="20">
-        <v>204.67</v>
+        <v>28.4</v>
       </c>
       <c r="AA38"/>
       <c r="AB38"/>
       <c r="AC38" s="15"/>
       <c r="AD38" s="19">
-        <v>208</v>
+        <v>53</v>
       </c>
       <c r="AE38" s="15">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AF38" s="21">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AG38" s="22">
-        <v>0</v>
+        <v>0.032799999999999996</v>
       </c>
       <c r="AH38" s="20">
-        <v>11.24</v>
+        <v>11.12</v>
       </c>
       <c r="AI38" s="16">
-        <v>0.81</v>
+        <v>0.46</v>
       </c>
       <c r="AJ38"/>
       <c r="AK38" s="13" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2017-12-18</t>
         </is>
       </c>
       <c r="AL38" s="19">
-        <v>960</v>
+        <v>3215</v>
       </c>
       <c r="AM38" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN38" s="13"/>
@@ -16006,17 +15896,29 @@
       </c>
       <c r="AS38" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>DistriPro</t>
         </is>
       </c>
       <c r="AT38" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU38" s="13"/>
-      <c r="AV38" s="14"/>
-      <c r="AW38" s="13"/>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU38" s="13" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="AV38" s="14" t="inlineStr">
+        <is>
+          <t>Grisy Suisnes 77166 FR</t>
+        </is>
+      </c>
+      <c r="AW38" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AMPFK1KKUPHEA</t>
+        </is>
+      </c>
       <c r="AX38" s="13"/>
       <c r="AY38" s="13"/>
       <c r="AZ38" s="13"/>
@@ -16039,41 +15941,37 @@
       <c r="BI38" s="23"/>
       <c r="BJ38" s="23" t="inlineStr">
         <is>
-          <t>7,71 Kilogrammes</t>
-        </is>
-      </c>
-      <c r="BK38" s="23"/>
+          <t>200 grammes</t>
+        </is>
+      </c>
+      <c r="BK38" s="23" t="inlineStr">
+        <is>
+          <t>200.00 g</t>
+        </is>
+      </c>
       <c r="BL38" s="23" t="inlineStr">
         <is>
-          <t>42P x 30l x 108H centimètres</t>
-        </is>
-      </c>
-      <c r="BM38" s="23"/>
+          <t>18 x 14 x 25 cm</t>
+        </is>
+      </c>
+      <c r="BM38" s="23" t="inlineStr">
+        <is>
+          <t>18.00 x 14.00 x 25.00 cm</t>
+        </is>
+      </c>
       <c r="BN38" s="23" t="inlineStr">
         <is>
-          <t>11.05 kg</t>
+          <t>200 g</t>
         </is>
       </c>
       <c r="BO38" s="23" t="inlineStr">
         <is>
-          <t>11.05 kg</t>
-        </is>
-      </c>
-      <c r="BP38" s="23" t="inlineStr">
-        <is>
-          <t>63 x 45 x 32.5 cm</t>
-        </is>
-      </c>
-      <c r="BQ38" s="23" t="inlineStr">
-        <is>
-          <t>63.00 x 45.00 x 32.50 cm</t>
-        </is>
-      </c>
-      <c r="BR38" s="13" t="inlineStr">
-        <is>
-          <t>轻型标准大件</t>
-        </is>
-      </c>
+          <t>200.00 g</t>
+        </is>
+      </c>
+      <c r="BP38" s="23"/>
+      <c r="BQ38" s="23"/>
+      <c r="BR38" s="13"/>
     </row>
     <row r="39" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="13">
@@ -16082,40 +15980,40 @@
       <c r="B39" s="13"/>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>B01HZUX61M</t>
+          <t>B0FFHS6LWS</t>
         </is>
       </c>
       <c r="D39" s="14"/>
       <c r="E39" s="14"/>
       <c r="F39" s="14" t="inlineStr">
         <is>
-          <t>Tech'N'Fast</t>
+          <t>Olvy</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/Technfast/page/5C561153-C96A-4DCF-BA10-143B211F8707?lp_asin=B01HZUX61M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.fr/stores/OLVY/page/0323FB43-67E5-4EBB-83A3-4CA8B62531C9?lp_asin=B0FFHS6LWS&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>Nettoyant textile concentré, canapé, moquette, tapis, sièges auto, détachant, dissout les tâches et neutralise les odeurs - B</t>
+          <t>Olvy Aspirateur Balai sans Fil Nettoyeur Puissant 350W Dark Blue 35KPa PuresMénage facile | Aspiration forte anti-crochets</t>
         </is>
       </c>
       <c r="I39" s="14"/>
       <c r="J39" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B01HZUX61M?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0FFHS6LWS?psc=1</t>
         </is>
       </c>
       <c r="K39" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/319Ry9yZeTL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41GxuZ621XL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L39" s="14" t="inlineStr">
         <is>
-          <t>B01HZUX61M</t>
+          <t>B0FFHS6LWS</t>
         </is>
       </c>
       <c r="M39" s="14" t="inlineStr">
@@ -16129,13 +16027,13 @@
         </is>
       </c>
       <c r="O39" s="15">
-        <v>16042</v>
+        <v>25659</v>
       </c>
       <c r="P39" s="15">
-        <v>-3040</v>
+        <v>-3022</v>
       </c>
       <c r="Q39" s="16">
-        <v>-0.21</v>
+        <v>-0.08</v>
       </c>
       <c r="R39" s="17" t="inlineStr">
         <is>
@@ -16144,61 +16042,55 @@
       </c>
       <c r="S39" s="18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>36</t>
         </is>
       </c>
       <c r="T39" s="15">
-        <v>183</v>
+        <v>66</v>
       </c>
       <c r="U39" s="16">
-        <v>0.13</v>
+        <v>-0.61</v>
       </c>
       <c r="V39" s="15">
-        <v>5197</v>
-      </c>
-      <c r="W39" s="15" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="X39" s="15">
-        <v>3416</v>
-      </c>
+        <v>5048</v>
+      </c>
+      <c r="W39" s="15"/>
+      <c r="X39" s="15"/>
       <c r="Y39" s="19">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Z39" s="20">
-        <v>28.4</v>
+        <v>76.49</v>
       </c>
       <c r="AA39"/>
       <c r="AB39"/>
       <c r="AC39" s="15"/>
       <c r="AD39" s="19">
-        <v>53</v>
+        <v>282</v>
       </c>
       <c r="AE39" s="15">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AF39" s="21">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AG39" s="22">
-        <v>0.032799999999999996</v>
+        <v>0</v>
       </c>
       <c r="AH39" s="20">
-        <v>11.12</v>
+        <v>8.44</v>
       </c>
       <c r="AI39" s="16">
-        <v>0.46</v>
+        <v>0.76</v>
       </c>
       <c r="AJ39"/>
       <c r="AK39" s="13" t="inlineStr">
         <is>
-          <t>2017-12-18</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AL39" s="19">
-        <v>3215</v>
+        <v>462</v>
       </c>
       <c r="AM39" s="13" t="inlineStr">
         <is>
@@ -16212,11 +16104,11 @@
         <v>10</v>
       </c>
       <c r="AR39" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS39" s="14" t="inlineStr">
         <is>
-          <t>DistriPro</t>
+          <t>Olvy</t>
         </is>
       </c>
       <c r="AT39" s="13" t="inlineStr">
@@ -16226,21 +16118,25 @@
       </c>
       <c r="AU39" s="13" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="AV39" s="14" t="inlineStr">
         <is>
-          <t>Grisy Suisnes 77166 FR</t>
+          <t>NIJMEGEN Gelderland 6511DX NL</t>
         </is>
       </c>
       <c r="AW39" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AMPFK1KKUPHEA</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A7NHEBYLM424G</t>
         </is>
       </c>
       <c r="AX39" s="13"/>
-      <c r="AY39" s="13"/>
+      <c r="AY39" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ39" s="13"/>
       <c r="BA39" s="13"/>
       <c r="BB39" s="13"/>
@@ -16258,40 +16154,52 @@
       <c r="BF39" s="13"/>
       <c r="BG39" s="13"/>
       <c r="BH39" s="14"/>
-      <c r="BI39" s="23"/>
+      <c r="BI39" s="23" t="inlineStr">
+        <is>
+          <t>Choix d'Amazon</t>
+        </is>
+      </c>
       <c r="BJ39" s="23" t="inlineStr">
         <is>
-          <t>200 grammes</t>
+          <t>3,86 Kilograms</t>
         </is>
       </c>
       <c r="BK39" s="23" t="inlineStr">
         <is>
-          <t>200.00 g</t>
+          <t>3.86 kg</t>
         </is>
       </c>
       <c r="BL39" s="23" t="inlineStr">
         <is>
-          <t>18 x 14 x 25 cm</t>
-        </is>
-      </c>
-      <c r="BM39" s="23" t="inlineStr">
-        <is>
-          <t>18.00 x 14.00 x 25.00 cm</t>
-        </is>
-      </c>
+          <t>23L x 25l x 11,8H centimètres</t>
+        </is>
+      </c>
+      <c r="BM39" s="23"/>
       <c r="BN39" s="23" t="inlineStr">
         <is>
-          <t>200 g</t>
+          <t>3.86 kg</t>
         </is>
       </c>
       <c r="BO39" s="23" t="inlineStr">
         <is>
-          <t>200.00 g</t>
-        </is>
-      </c>
-      <c r="BP39" s="23"/>
-      <c r="BQ39" s="23"/>
-      <c r="BR39" s="13"/>
+          <t>3.86 kg</t>
+        </is>
+      </c>
+      <c r="BP39" s="23" t="inlineStr">
+        <is>
+          <t>44.8 x 26.3 x 19.9 cm</t>
+        </is>
+      </c>
+      <c r="BQ39" s="23" t="inlineStr">
+        <is>
+          <t>44.80 x 26.30 x 19.90 cm</t>
+        </is>
+      </c>
+      <c r="BR39" s="13" t="inlineStr">
+        <is>
+          <t>标准包裹</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="13">
@@ -16300,40 +16208,40 @@
       <c r="B40" s="13"/>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>B0FFHS6LWS</t>
+          <t>B0CLYF3DMZ</t>
         </is>
       </c>
       <c r="D40" s="14"/>
       <c r="E40" s="14"/>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>Olvy</t>
+          <t>LEHMANN</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/OLVY/page/0323FB43-67E5-4EBB-83A3-4CA8B62531C9?lp_asin=B0FFHS6LWS&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.fr/stores/LEHMANN/page/EAB8CEA1-93E8-4C19-BC95-67B7BFD404B9?lp_asin=B0CLYF3DMZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>Olvy Aspirateur Balai sans Fil Nettoyeur Puissant 350W Dark Blue 35KPa PuresMénage facile | Aspiration forte anti-crochets</t>
+          <t>Lehmann Prowash 2000 Professionnel Aspirateur Nettoyeur, Multifonction Shampouineuse Idéal pour Canapé, Tapis, Rembourrage, V</t>
         </is>
       </c>
       <c r="I40" s="14"/>
       <c r="J40" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0FFHS6LWS?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0CLYF3DMZ?psc=1</t>
         </is>
       </c>
       <c r="K40" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41GxuZ621XL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41R8Ql2gj9L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>B0FFHS6LWS</t>
+          <t>B0CLYF3DMZ</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
@@ -16347,13 +16255,13 @@
         </is>
       </c>
       <c r="O40" s="15">
-        <v>25659</v>
+        <v>48592</v>
       </c>
       <c r="P40" s="15">
-        <v>-3022</v>
+        <v>-29558</v>
       </c>
       <c r="Q40" s="16">
-        <v>-0.08</v>
+        <v>-0.84</v>
       </c>
       <c r="R40" s="17" t="inlineStr">
         <is>
@@ -16362,59 +16270,59 @@
       </c>
       <c r="S40" s="18" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>49</t>
         </is>
       </c>
       <c r="T40" s="15">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="U40" s="16">
-        <v>-0.61</v>
+        <v>3.53</v>
       </c>
       <c r="V40" s="15">
-        <v>5048</v>
+        <v>4950</v>
       </c>
       <c r="W40" s="15"/>
       <c r="X40" s="15"/>
       <c r="Y40" s="19">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z40" s="20">
-        <v>76.49</v>
+        <v>98.99</v>
       </c>
       <c r="AA40"/>
       <c r="AB40"/>
       <c r="AC40" s="15"/>
       <c r="AD40" s="19">
-        <v>282</v>
+        <v>392</v>
       </c>
       <c r="AE40" s="15">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AF40" s="21">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AG40" s="22">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AH40" s="20">
-        <v>8.44</v>
+        <v>9.96</v>
       </c>
       <c r="AI40" s="16">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="AJ40"/>
       <c r="AK40" s="13" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="AL40" s="19">
-        <v>462</v>
+        <v>932</v>
       </c>
       <c r="AM40" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AN40" s="13"/>
@@ -16424,31 +16332,31 @@
         <v>10</v>
       </c>
       <c r="AR40" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS40" s="14" t="inlineStr">
         <is>
-          <t>Olvy</t>
+          <t>Lehmann HG</t>
         </is>
       </c>
       <c r="AT40" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AU40" s="13" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="AV40" s="14" t="inlineStr">
         <is>
-          <t>NIJMEGEN Gelderland 6511DX NL</t>
+          <t>Greater Poland 63-100 PL</t>
         </is>
       </c>
       <c r="AW40" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A7NHEBYLM424G</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH</t>
         </is>
       </c>
       <c r="AX40" s="13"/>
@@ -16465,11 +16373,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD40" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD40" s="13"/>
       <c r="BE40" s="13"/>
       <c r="BF40" s="13"/>
       <c r="BG40" s="13"/>
@@ -16481,43 +16385,43 @@
       </c>
       <c r="BJ40" s="23" t="inlineStr">
         <is>
-          <t>3,86 Kilograms</t>
+          <t>6,2 Kilograms</t>
         </is>
       </c>
       <c r="BK40" s="23" t="inlineStr">
         <is>
-          <t>3.86 kg</t>
+          <t>6.20 kg</t>
         </is>
       </c>
       <c r="BL40" s="23" t="inlineStr">
         <is>
-          <t>23L x 25l x 11,8H centimètres</t>
+          <t>51,3P x 27,5l x 28,8H centimètres</t>
         </is>
       </c>
       <c r="BM40" s="23"/>
       <c r="BN40" s="23" t="inlineStr">
         <is>
-          <t>3.86 kg</t>
+          <t>7.77 kg</t>
         </is>
       </c>
       <c r="BO40" s="23" t="inlineStr">
         <is>
-          <t>3.86 kg</t>
+          <t>7.77 kg</t>
         </is>
       </c>
       <c r="BP40" s="23" t="inlineStr">
         <is>
-          <t>44.8 x 26.3 x 19.9 cm</t>
+          <t>54.8 x 37.1 x 30.8 cm</t>
         </is>
       </c>
       <c r="BQ40" s="23" t="inlineStr">
         <is>
-          <t>44.80 x 26.30 x 19.90 cm</t>
+          <t>54.80 x 37.10 x 30.80 cm</t>
         </is>
       </c>
       <c r="BR40" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -16528,40 +16432,40 @@
       <c r="B41" s="13"/>
       <c r="C41" s="14" t="inlineStr">
         <is>
-          <t>B0CLYF3DMZ</t>
+          <t>B0B3J3Q9RD</t>
         </is>
       </c>
       <c r="D41" s="14"/>
       <c r="E41" s="14"/>
       <c r="F41" s="14" t="inlineStr">
         <is>
-          <t>LEHMANN</t>
+          <t>HAUSHOF</t>
         </is>
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/LEHMANN/page/EAB8CEA1-93E8-4C19-BC95-67B7BFD404B9?lp_asin=B0CLYF3DMZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.fr/stores/HAUSHOF/page/F29AB38F-2156-4E8D-8FE4-F22692B62A19?lp_asin=B0B3J3Q9RD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
-          <t>Lehmann Prowash 2000 Professionnel Aspirateur Nettoyeur, Multifonction Shampouineuse Idéal pour Canapé, Tapis, Rembourrage, V</t>
+          <t>HAUSHOF StainZapper Shampouineuse 400 W avec Double RéservoirsNettoyeur de Tapis, Réservoirs 1,1 L + 0,5 L, Tuyau 1,2 m, 2</t>
         </is>
       </c>
       <c r="I41" s="14"/>
       <c r="J41" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0CLYF3DMZ?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0B3J3Q9RD?psc=1</t>
         </is>
       </c>
       <c r="K41" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41R8Ql2gj9L._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71xJpcYtPpL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L41" s="14" t="inlineStr">
         <is>
-          <t>B0CLYF3DMZ</t>
+          <t>B0B3J3Q9RD</t>
         </is>
       </c>
       <c r="M41" s="14" t="inlineStr">
@@ -16575,13 +16479,13 @@
         </is>
       </c>
       <c r="O41" s="15">
-        <v>48592</v>
+        <v>27144</v>
       </c>
       <c r="P41" s="15">
-        <v>-29558</v>
+        <v>5985</v>
       </c>
       <c r="Q41" s="16">
-        <v>-0.84</v>
+        <v>0.18</v>
       </c>
       <c r="R41" s="17" t="inlineStr">
         <is>
@@ -16590,17 +16494,17 @@
       </c>
       <c r="S41" s="18" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>35</t>
         </is>
       </c>
       <c r="T41" s="15">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="U41" s="16">
-        <v>3.53</v>
+        <v>-0.3</v>
       </c>
       <c r="V41" s="15">
-        <v>4950</v>
+        <v>4850</v>
       </c>
       <c r="W41" s="15"/>
       <c r="X41" s="15"/>
@@ -16608,41 +16512,41 @@
         <v>1</v>
       </c>
       <c r="Z41" s="20">
-        <v>98.99</v>
+        <v>69.99</v>
       </c>
       <c r="AA41"/>
       <c r="AB41"/>
       <c r="AC41" s="15"/>
       <c r="AD41" s="19">
-        <v>392</v>
+        <v>4835</v>
       </c>
       <c r="AE41" s="15">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="AF41" s="21">
         <v>4.2</v>
       </c>
       <c r="AG41" s="22">
-        <v>0.12</v>
+        <v>0.2297</v>
       </c>
       <c r="AH41" s="20">
-        <v>9.96</v>
+        <v>8.47</v>
       </c>
       <c r="AI41" s="16">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="AJ41"/>
       <c r="AK41" s="13" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AL41" s="19">
-        <v>932</v>
+        <v>1268</v>
       </c>
       <c r="AM41" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN41" s="13"/>
@@ -16652,33 +16556,21 @@
         <v>10</v>
       </c>
       <c r="AR41" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS41" s="14" t="inlineStr">
         <is>
-          <t>Lehmann HG</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT41" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
-        </is>
-      </c>
-      <c r="AU41" s="13" t="inlineStr">
-        <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="AV41" s="14" t="inlineStr">
-        <is>
-          <t>Greater Poland 63-100 PL</t>
-        </is>
-      </c>
-      <c r="AW41" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH</t>
-        </is>
-      </c>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU41" s="13"/>
+      <c r="AV41" s="14"/>
+      <c r="AW41" s="13"/>
       <c r="AX41" s="13"/>
       <c r="AY41" s="13" t="inlineStr">
         <is>
@@ -16693,7 +16585,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD41" s="13"/>
+      <c r="BD41" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE41" s="13"/>
       <c r="BF41" s="13"/>
       <c r="BG41" s="13"/>
@@ -16705,38 +16601,42 @@
       </c>
       <c r="BJ41" s="23" t="inlineStr">
         <is>
-          <t>6,2 Kilograms</t>
+          <t>3.4 kg</t>
         </is>
       </c>
       <c r="BK41" s="23" t="inlineStr">
         <is>
-          <t>6.20 kg</t>
+          <t>3.40 kg</t>
         </is>
       </c>
       <c r="BL41" s="23" t="inlineStr">
         <is>
-          <t>51,3P x 27,5l x 28,8H centimètres</t>
-        </is>
-      </c>
-      <c r="BM41" s="23"/>
+          <t>15.2 x 28.5 x 26.5 cm</t>
+        </is>
+      </c>
+      <c r="BM41" s="23" t="inlineStr">
+        <is>
+          <t>15.20 x 28.50 x 26.50 cm</t>
+        </is>
+      </c>
       <c r="BN41" s="23" t="inlineStr">
         <is>
-          <t>7.77 kg</t>
+          <t>4.85 kg</t>
         </is>
       </c>
       <c r="BO41" s="23" t="inlineStr">
         <is>
-          <t>7.77 kg</t>
+          <t>4.85 kg</t>
         </is>
       </c>
       <c r="BP41" s="23" t="inlineStr">
         <is>
-          <t>54.8 x 37.1 x 30.8 cm</t>
+          <t>40.2 x 34.2 x 19.5 cm</t>
         </is>
       </c>
       <c r="BQ41" s="23" t="inlineStr">
         <is>
-          <t>54.80 x 37.10 x 30.80 cm</t>
+          <t>40.20 x 34.20 x 19.50 cm</t>
         </is>
       </c>
       <c r="BR41" s="13" t="inlineStr">
@@ -16752,40 +16652,40 @@
       <c r="B42" s="13"/>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>B0B3J3Q9RD</t>
+          <t>B0HFW8M5VH</t>
         </is>
       </c>
       <c r="D42" s="14"/>
       <c r="E42" s="14"/>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>HAUSHOF</t>
+          <t>uwant</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/HAUSHOF/page/F29AB38F-2156-4E8D-8FE4-F22692B62A19?lp_asin=B0B3J3Q9RD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.fr/stores/uwant/page/22E764CF-7C20-4A56-AAA4-4DCFB8ECAC57?lp_asin=B0HFW8M5VH&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>HAUSHOF StainZapper Shampouineuse 400 W avec Double RéservoirsNettoyeur de Tapis, Réservoirs 1,1 L + 0,5 L, Tuyau 1,2 m, 2</t>
+          <t>Uwant Y100S Shampouineuse, Lave et Sèche, 1750W, 18kPa, Réservoir 2.4L.sTuyau Autonettoyant, Vapeur Chaude Lave Facile, Bro</t>
         </is>
       </c>
       <c r="I42" s="14"/>
       <c r="J42" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0B3J3Q9RD?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0HFW8M5VH?psc=1</t>
         </is>
       </c>
       <c r="K42" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71xJpcYtPpL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/411+BeEHvHL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>B0B3J3Q9RD</t>
+          <t>B0HFW8M5VH</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
@@ -16799,13 +16699,13 @@
         </is>
       </c>
       <c r="O42" s="15">
-        <v>27144</v>
+        <v>39923</v>
       </c>
       <c r="P42" s="15">
-        <v>5985</v>
+        <v>39529</v>
       </c>
       <c r="Q42" s="16">
-        <v>0.18</v>
+        <v>0.57</v>
       </c>
       <c r="R42" s="17" t="inlineStr">
         <is>
@@ -16814,89 +16714,95 @@
       </c>
       <c r="S42" s="18" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>50</t>
         </is>
       </c>
       <c r="T42" s="15">
-        <v>74</v>
-      </c>
-      <c r="U42" s="16">
-        <v>-0.3</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="U42" s="16"/>
       <c r="V42" s="15">
-        <v>4850</v>
+        <v>4800</v>
       </c>
       <c r="W42" s="15"/>
       <c r="X42" s="15"/>
       <c r="Y42" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z42" s="20">
-        <v>69.99</v>
+        <v>149.99</v>
       </c>
       <c r="AA42"/>
       <c r="AB42"/>
       <c r="AC42" s="15"/>
       <c r="AD42" s="19">
-        <v>4835</v>
+        <v>265</v>
       </c>
       <c r="AE42" s="15">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AF42" s="21">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AG42" s="22">
-        <v>0.2297</v>
+        <v>0</v>
       </c>
       <c r="AH42" s="20">
-        <v>8.47</v>
+        <v>9.32</v>
       </c>
       <c r="AI42" s="16">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="AJ42"/>
       <c r="AK42" s="13" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AL42" s="19">
-        <v>1268</v>
+        <v>41</v>
       </c>
       <c r="AM42" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN42" s="13"/>
       <c r="AO42" s="13"/>
       <c r="AP42"/>
       <c r="AQ42" s="19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR42" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS42" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>TIMO Smart Home</t>
         </is>
       </c>
       <c r="AT42" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU42" s="13"/>
-      <c r="AV42" s="14"/>
-      <c r="AW42" s="13"/>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="AU42" s="13" t="inlineStr">
+        <is>
+          <t>CN(HK)</t>
+        </is>
+      </c>
+      <c r="AV42" s="14" t="inlineStr">
+        <is>
+          <t>KWUN TONG KOWLOON 999077 HK</t>
+        </is>
+      </c>
+      <c r="AW42" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AR2TXP04XQ1UK</t>
+        </is>
+      </c>
       <c r="AX42" s="13"/>
-      <c r="AY42" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY42" s="13"/>
       <c r="AZ42" s="13"/>
       <c r="BA42" s="13"/>
       <c r="BB42" s="13"/>
@@ -16914,49 +16820,37 @@
       <c r="BF42" s="13"/>
       <c r="BG42" s="13"/>
       <c r="BH42" s="14"/>
-      <c r="BI42" s="23" t="inlineStr">
-        <is>
-          <t>Choix d'Amazon</t>
-        </is>
-      </c>
+      <c r="BI42" s="23"/>
       <c r="BJ42" s="23" t="inlineStr">
         <is>
-          <t>3.4 kg</t>
-        </is>
-      </c>
-      <c r="BK42" s="23" t="inlineStr">
-        <is>
-          <t>3.40 kg</t>
-        </is>
-      </c>
+          <t>2,5 Kilogrammes</t>
+        </is>
+      </c>
+      <c r="BK42" s="23"/>
       <c r="BL42" s="23" t="inlineStr">
         <is>
-          <t>15.2 x 28.5 x 26.5 cm</t>
-        </is>
-      </c>
-      <c r="BM42" s="23" t="inlineStr">
-        <is>
-          <t>15.20 x 28.50 x 26.50 cm</t>
-        </is>
-      </c>
+          <t>25P x 45l x 35H millimètres</t>
+        </is>
+      </c>
+      <c r="BM42" s="23"/>
       <c r="BN42" s="23" t="inlineStr">
         <is>
-          <t>4.85 kg</t>
+          <t>6.26 kg</t>
         </is>
       </c>
       <c r="BO42" s="23" t="inlineStr">
         <is>
-          <t>4.85 kg</t>
+          <t>6.26 kg</t>
         </is>
       </c>
       <c r="BP42" s="23" t="inlineStr">
         <is>
-          <t>40.2 x 34.2 x 19.5 cm</t>
+          <t>48 x 37.2 x 26.6 cm</t>
         </is>
       </c>
       <c r="BQ42" s="23" t="inlineStr">
         <is>
-          <t>40.20 x 34.20 x 19.50 cm</t>
+          <t>48.00 x 37.20 x 26.60 cm</t>
         </is>
       </c>
       <c r="BR42" s="13" t="inlineStr">
@@ -16972,40 +16866,40 @@
       <c r="B43" s="13"/>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>B0HFW8M5VH</t>
+          <t>B0FH4QL9GN</t>
         </is>
       </c>
       <c r="D43" s="14"/>
       <c r="E43" s="14"/>
       <c r="F43" s="14" t="inlineStr">
         <is>
-          <t>uwant</t>
+          <t>Livatro</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/uwant/page/22E764CF-7C20-4A56-AAA4-4DCFB8ECAC57?lp_asin=B0HFW8M5VH&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.fr/stores/Livatro/page/291E7715-1BBB-4063-93C4-B0F4B3739CDD?lp_asin=B0FH4QL9GN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>Uwant Y100S Shampouineuse, Lave et Sèche, 1750W, 18kPa, Réservoir 2.4L.sTuyau Autonettoyant, Vapeur Chaude Lave Facile, Bro</t>
+          <t>Livatro Shampouineuse Canapé avec Grand Réservoir pour Tissus et TapissEau propre 2,3 L, eau sale 1,3 L pour nettoyer plus</t>
         </is>
       </c>
       <c r="I43" s="14"/>
       <c r="J43" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0HFW8M5VH?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0FH4QL9GN?psc=1</t>
         </is>
       </c>
       <c r="K43" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/411+BeEHvHL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41OIdOf0WOL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L43" s="14" t="inlineStr">
         <is>
-          <t>B0HFW8M5VH</t>
+          <t>B0FH4QL9GN</t>
         </is>
       </c>
       <c r="M43" s="14" t="inlineStr">
@@ -17019,13 +16913,13 @@
         </is>
       </c>
       <c r="O43" s="15">
-        <v>39923</v>
+        <v>38428</v>
       </c>
       <c r="P43" s="15">
-        <v>39529</v>
+        <v>-13664</v>
       </c>
       <c r="Q43" s="16">
-        <v>0.57</v>
+        <v>-0.51</v>
       </c>
       <c r="R43" s="17" t="inlineStr">
         <is>
@@ -17034,53 +16928,61 @@
       </c>
       <c r="S43" s="18" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="T43" s="15">
+        <v>69</v>
+      </c>
+      <c r="U43" s="16">
+        <v>-0.29</v>
+      </c>
+      <c r="V43" s="15">
+        <v>4731</v>
+      </c>
+      <c r="W43" s="15" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="T43" s="15">
-        <v>32</v>
-      </c>
-      <c r="U43" s="16"/>
-      <c r="V43" s="15">
-        <v>4800</v>
-      </c>
-      <c r="W43" s="15"/>
-      <c r="X43" s="15"/>
+      <c r="X43" s="15">
+        <v>3848</v>
+      </c>
       <c r="Y43" s="19">
         <v>2</v>
       </c>
       <c r="Z43" s="20">
-        <v>149.99</v>
+        <v>68.57</v>
       </c>
       <c r="AA43"/>
       <c r="AB43"/>
       <c r="AC43" s="15"/>
       <c r="AD43" s="19">
-        <v>265</v>
+        <v>309</v>
       </c>
       <c r="AE43" s="15">
         <v>0</v>
       </c>
       <c r="AF43" s="21">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AG43" s="22">
         <v>0</v>
       </c>
       <c r="AH43" s="20">
-        <v>9.32</v>
+        <v>8.68</v>
       </c>
       <c r="AI43" s="16">
-        <v>0.8</v>
+        <v>0.72</v>
       </c>
       <c r="AJ43"/>
       <c r="AK43" s="13" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AL43" s="19">
-        <v>41</v>
+        <v>408</v>
       </c>
       <c r="AM43" s="13" t="inlineStr">
         <is>
@@ -17091,14 +16993,14 @@
       <c r="AO43" s="13"/>
       <c r="AP43"/>
       <c r="AQ43" s="19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR43" s="19">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AS43" s="14" t="inlineStr">
         <is>
-          <t>TIMO Smart Home</t>
+          <t>Kayon International</t>
         </is>
       </c>
       <c r="AT43" s="13" t="inlineStr">
@@ -17113,16 +17015,20 @@
       </c>
       <c r="AV43" s="14" t="inlineStr">
         <is>
-          <t>KWUN TONG KOWLOON 999077 HK</t>
+          <t>HONGKONG 999077 HK</t>
         </is>
       </c>
       <c r="AW43" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AR2TXP04XQ1UK</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1GEHAEQGC953B</t>
         </is>
       </c>
       <c r="AX43" s="13"/>
-      <c r="AY43" s="13"/>
+      <c r="AY43" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ43" s="13"/>
       <c r="BA43" s="13"/>
       <c r="BB43" s="13"/>
@@ -17140,37 +17046,45 @@
       <c r="BF43" s="13"/>
       <c r="BG43" s="13"/>
       <c r="BH43" s="14"/>
-      <c r="BI43" s="23"/>
+      <c r="BI43" s="23" t="inlineStr">
+        <is>
+          <t>Choix d'Amazon</t>
+        </is>
+      </c>
       <c r="BJ43" s="23" t="inlineStr">
         <is>
-          <t>2,5 Kilogrammes</t>
-        </is>
-      </c>
-      <c r="BK43" s="23"/>
+          <t>3,8 Kilograms</t>
+        </is>
+      </c>
+      <c r="BK43" s="23" t="inlineStr">
+        <is>
+          <t>3.80 kg</t>
+        </is>
+      </c>
       <c r="BL43" s="23" t="inlineStr">
         <is>
-          <t>25P x 45l x 35H millimètres</t>
+          <t>22,9P x 37l x 35,6H centimètres</t>
         </is>
       </c>
       <c r="BM43" s="23"/>
       <c r="BN43" s="23" t="inlineStr">
         <is>
-          <t>6.26 kg</t>
+          <t>4.66 kg</t>
         </is>
       </c>
       <c r="BO43" s="23" t="inlineStr">
         <is>
-          <t>6.26 kg</t>
+          <t>4.66 kg</t>
         </is>
       </c>
       <c r="BP43" s="23" t="inlineStr">
         <is>
-          <t>48 x 37.2 x 26.6 cm</t>
+          <t>45.1 x 36.6 x 20.5 cm</t>
         </is>
       </c>
       <c r="BQ43" s="23" t="inlineStr">
         <is>
-          <t>48.00 x 37.20 x 26.60 cm</t>
+          <t>45.10 x 36.60 x 20.50 cm</t>
         </is>
       </c>
       <c r="BR43" s="13" t="inlineStr">
@@ -17186,40 +17100,40 @@
       <c r="B44" s="13"/>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>B0FH4QL9GN</t>
+          <t>B0BSHCQQ4W</t>
         </is>
       </c>
       <c r="D44" s="14"/>
       <c r="E44" s="14"/>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>Livatro</t>
+          <t>H.Koenig</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/Livatro/page/291E7715-1BBB-4063-93C4-B0F4B3739CDD?lp_asin=B0FH4QL9GN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.fr/stores/HKoenig/page/58E8DB4A-AF96-40E3-AB82-3B5DA9F75657?lp_asin=B0BSHCQQ4W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>Livatro Shampouineuse Canapé avec Grand Réservoir pour Tissus et TapissEau propre 2,3 L, eau sale 1,3 L pour nettoyer plus</t>
+          <t>H.Koenig Nettoyeur Détacheur TWT77, Shampouineuse, Nettoyeur Tapis Canapé et Tissu, Double Réservoir, Brosse de Rechange Incl</t>
         </is>
       </c>
       <c r="I44" s="14"/>
       <c r="J44" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0FH4QL9GN?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0BSHCQQ4W?psc=1</t>
         </is>
       </c>
       <c r="K44" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41OIdOf0WOL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61W1ckv75YL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>B0FH4QL9GN</t>
+          <t>B0BSHCQQ4W</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
@@ -17233,13 +17147,13 @@
         </is>
       </c>
       <c r="O44" s="15">
-        <v>38428</v>
+        <v>18171</v>
       </c>
       <c r="P44" s="15">
-        <v>-13664</v>
+        <v>23832</v>
       </c>
       <c r="Q44" s="16">
-        <v>-0.51</v>
+        <v>0.57</v>
       </c>
       <c r="R44" s="17" t="inlineStr">
         <is>
@@ -17248,61 +17162,55 @@
       </c>
       <c r="S44" s="18" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>29</t>
         </is>
       </c>
       <c r="T44" s="15">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="U44" s="16">
-        <v>-0.29</v>
+        <v>-0.3</v>
       </c>
       <c r="V44" s="15">
-        <v>4731</v>
-      </c>
-      <c r="W44" s="15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X44" s="15">
-        <v>3848</v>
-      </c>
+        <v>3578</v>
+      </c>
+      <c r="W44" s="15"/>
+      <c r="X44" s="15"/>
       <c r="Y44" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z44" s="20">
-        <v>68.57</v>
+        <v>63.9</v>
       </c>
       <c r="AA44"/>
       <c r="AB44"/>
       <c r="AC44" s="15"/>
       <c r="AD44" s="19">
-        <v>309</v>
+        <v>1081</v>
       </c>
       <c r="AE44" s="15">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AF44" s="21">
         <v>4.2</v>
       </c>
       <c r="AG44" s="22">
-        <v>0</v>
+        <v>0.1429</v>
       </c>
       <c r="AH44" s="20">
-        <v>8.68</v>
+        <v>9.53</v>
       </c>
       <c r="AI44" s="16">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="AJ44"/>
       <c r="AK44" s="13" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2023-02-19</t>
         </is>
       </c>
       <c r="AL44" s="19">
-        <v>408</v>
+        <v>1327</v>
       </c>
       <c r="AM44" s="13" t="inlineStr">
         <is>
@@ -17316,11 +17224,11 @@
         <v>10</v>
       </c>
       <c r="AR44" s="19">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AS44" s="14" t="inlineStr">
         <is>
-          <t>Kayon International</t>
+          <t>HomeHome by A</t>
         </is>
       </c>
       <c r="AT44" s="13" t="inlineStr">
@@ -17330,17 +17238,17 @@
       </c>
       <c r="AU44" s="13" t="inlineStr">
         <is>
-          <t>CN(HK)</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="AV44" s="14" t="inlineStr">
         <is>
-          <t>HONGKONG 999077 HK</t>
+          <t>Paris 75001 FR</t>
         </is>
       </c>
       <c r="AW44" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1GEHAEQGC953B</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2J1ZXSJG29176</t>
         </is>
       </c>
       <c r="AX44" s="13"/>
@@ -17373,38 +17281,42 @@
       </c>
       <c r="BJ44" s="23" t="inlineStr">
         <is>
-          <t>3,8 Kilograms</t>
+          <t>4 kg</t>
         </is>
       </c>
       <c r="BK44" s="23" t="inlineStr">
         <is>
-          <t>3.80 kg</t>
+          <t>4.00 kg</t>
         </is>
       </c>
       <c r="BL44" s="23" t="inlineStr">
         <is>
-          <t>22,9P x 37l x 35,6H centimètres</t>
-        </is>
-      </c>
-      <c r="BM44" s="23"/>
+          <t>36.5 x 24.5 x 31.8 cm</t>
+        </is>
+      </c>
+      <c r="BM44" s="23" t="inlineStr">
+        <is>
+          <t>36.50 x 24.50 x 31.80 cm</t>
+        </is>
+      </c>
       <c r="BN44" s="23" t="inlineStr">
         <is>
-          <t>4.66 kg</t>
+          <t>5.88 kg</t>
         </is>
       </c>
       <c r="BO44" s="23" t="inlineStr">
         <is>
-          <t>4.66 kg</t>
+          <t>5.88 kg</t>
         </is>
       </c>
       <c r="BP44" s="23" t="inlineStr">
         <is>
-          <t>45.1 x 36.6 x 20.5 cm</t>
+          <t>45 x 38 x 29 cm</t>
         </is>
       </c>
       <c r="BQ44" s="23" t="inlineStr">
         <is>
-          <t>45.10 x 36.60 x 20.50 cm</t>
+          <t>45.00 x 38.00 x 29.00 cm</t>
         </is>
       </c>
       <c r="BR44" s="13" t="inlineStr">
@@ -17420,40 +17332,40 @@
       <c r="B45" s="13"/>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>B0BSHCQQ4W</t>
+          <t>B0FDL5FJ5W</t>
         </is>
       </c>
       <c r="D45" s="14"/>
       <c r="E45" s="14"/>
       <c r="F45" s="14" t="inlineStr">
         <is>
-          <t>H.Koenig</t>
+          <t>LEHMANN</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/HKoenig/page/58E8DB4A-AF96-40E3-AB82-3B5DA9F75657?lp_asin=B0BSHCQQ4W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.fr/stores/LEHMANN/page/EAB8CEA1-93E8-4C19-BC95-67B7BFD404B9?lp_asin=B0FDL5FJ5W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>H.Koenig Nettoyeur Détacheur TWT77, Shampouineuse, Nettoyeur Tapis Canapé et Tissu, Double Réservoir, Brosse de Rechange Incl</t>
+          <t>LEHMANN Shampouineuse avec Réservoir de 20L, 1600 W, Aspirateur Injecteur-extracteur avec filtre HEPA, Réservoir à détergent</t>
         </is>
       </c>
       <c r="I45" s="14"/>
       <c r="J45" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0BSHCQQ4W?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0FDL5FJ5W?psc=1</t>
         </is>
       </c>
       <c r="K45" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61W1ckv75YL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41CKqZHXRBL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L45" s="14" t="inlineStr">
         <is>
-          <t>B0BSHCQQ4W</t>
+          <t>B0FDL5FJ5W</t>
         </is>
       </c>
       <c r="M45" s="14" t="inlineStr">
@@ -17467,13 +17379,13 @@
         </is>
       </c>
       <c r="O45" s="15">
-        <v>18171</v>
+        <v>66226</v>
       </c>
       <c r="P45" s="15">
-        <v>23832</v>
+        <v>16541</v>
       </c>
       <c r="Q45" s="16">
-        <v>0.57</v>
+        <v>0.12</v>
       </c>
       <c r="R45" s="17" t="inlineStr">
         <is>
@@ -17482,101 +17394,97 @@
       </c>
       <c r="S45" s="18" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>56</t>
         </is>
       </c>
       <c r="T45" s="15">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="U45" s="16">
-        <v>-0.3</v>
+        <v>2.06</v>
       </c>
       <c r="V45" s="15">
-        <v>3578</v>
+        <v>3290</v>
       </c>
       <c r="W45" s="15"/>
       <c r="X45" s="15"/>
       <c r="Y45" s="19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z45" s="20">
-        <v>63.9</v>
+        <v>69.99</v>
       </c>
       <c r="AA45"/>
       <c r="AB45"/>
       <c r="AC45" s="15"/>
       <c r="AD45" s="19">
-        <v>1081</v>
+        <v>171</v>
       </c>
       <c r="AE45" s="15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AF45" s="21">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AG45" s="22">
-        <v>0.1429</v>
+        <v>0.1277</v>
       </c>
       <c r="AH45" s="20">
-        <v>9.53</v>
+        <v>10.6</v>
       </c>
       <c r="AI45" s="16">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AJ45"/>
       <c r="AK45" s="13" t="inlineStr">
         <is>
-          <t>2023-02-19</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="AL45" s="19">
-        <v>1327</v>
+        <v>475</v>
       </c>
       <c r="AM45" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AN45" s="13"/>
       <c r="AO45" s="13"/>
       <c r="AP45"/>
       <c r="AQ45" s="19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR45" s="19">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="AS45" s="14" t="inlineStr">
         <is>
-          <t>HomeHome by A</t>
+          <t>Lehmann HG</t>
         </is>
       </c>
       <c r="AT45" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AU45" s="13" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="AV45" s="14" t="inlineStr">
         <is>
-          <t>Paris 75001 FR</t>
+          <t>Greater Poland 63-100 PL</t>
         </is>
       </c>
       <c r="AW45" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2J1ZXSJG29176</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH</t>
         </is>
       </c>
       <c r="AX45" s="13"/>
-      <c r="AY45" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY45" s="13"/>
       <c r="AZ45" s="13"/>
       <c r="BA45" s="13"/>
       <c r="BB45" s="13"/>
@@ -17585,58 +17493,46 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD45" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD45" s="13"/>
       <c r="BE45" s="13"/>
       <c r="BF45" s="13"/>
       <c r="BG45" s="13"/>
       <c r="BH45" s="14"/>
-      <c r="BI45" s="23" t="inlineStr">
-        <is>
-          <t>Choix d'Amazon</t>
-        </is>
-      </c>
+      <c r="BI45" s="23"/>
       <c r="BJ45" s="23" t="inlineStr">
         <is>
-          <t>4 kg</t>
+          <t>7,8 Kilograms</t>
         </is>
       </c>
       <c r="BK45" s="23" t="inlineStr">
         <is>
-          <t>4.00 kg</t>
+          <t>7.80 kg</t>
         </is>
       </c>
       <c r="BL45" s="23" t="inlineStr">
         <is>
-          <t>36.5 x 24.5 x 31.8 cm</t>
-        </is>
-      </c>
-      <c r="BM45" s="23" t="inlineStr">
-        <is>
-          <t>36.50 x 24.50 x 31.80 cm</t>
-        </is>
-      </c>
+          <t>44P x 36l x 51,5H centimètres</t>
+        </is>
+      </c>
+      <c r="BM45" s="23"/>
       <c r="BN45" s="23" t="inlineStr">
         <is>
-          <t>5.88 kg</t>
+          <t>8.8 kg</t>
         </is>
       </c>
       <c r="BO45" s="23" t="inlineStr">
         <is>
-          <t>5.88 kg</t>
+          <t>8.80 kg</t>
         </is>
       </c>
       <c r="BP45" s="23" t="inlineStr">
         <is>
-          <t>45 x 38 x 29 cm</t>
+          <t>55 x 39.5 x 36 cm</t>
         </is>
       </c>
       <c r="BQ45" s="23" t="inlineStr">
         <is>
-          <t>45.00 x 38.00 x 29.00 cm</t>
+          <t>55.00 x 39.50 x 36.00 cm</t>
         </is>
       </c>
       <c r="BR45" s="13" t="inlineStr">
@@ -17652,40 +17548,40 @@
       <c r="B46" s="13"/>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>B0FDL5FJ5W</t>
+          <t>B0FMG1PY3G</t>
         </is>
       </c>
       <c r="D46" s="14"/>
       <c r="E46" s="14"/>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>LEHMANN</t>
+          <t>Olvy</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/LEHMANN/page/EAB8CEA1-93E8-4C19-BC95-67B7BFD404B9?lp_asin=B0FDL5FJ5W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.fr/stores/OLVY/page/0323FB43-67E5-4EBB-83A3-4CA8B62531C9?lp_asin=B0FMG1PY3G&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>LEHMANN Shampouineuse avec Réservoir de 20L, 1600 W, Aspirateur Injecteur-extracteur avec filtre HEPA, Réservoir à détergent</t>
+          <t>Olvy Shampouineuse Canape Nettoyeur Tapis Injecteur Extracteurs1 Appareil | 17000 PA Aspiration Profonde | Tapis &amp; Moquette</t>
         </is>
       </c>
       <c r="I46" s="14"/>
       <c r="J46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0FDL5FJ5W?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0FMG1PY3G?psc=1</t>
         </is>
       </c>
       <c r="K46" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41CKqZHXRBL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41dgQOFmcHL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>B0FDL5FJ5W</t>
+          <t>B0FMG1PY3G</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
@@ -17699,13 +17595,13 @@
         </is>
       </c>
       <c r="O46" s="15">
-        <v>66226</v>
+        <v>15779</v>
       </c>
       <c r="P46" s="15">
-        <v>16541</v>
+        <v>4455</v>
       </c>
       <c r="Q46" s="16">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="R46" s="17" t="inlineStr">
         <is>
@@ -17714,97 +17610,101 @@
       </c>
       <c r="S46" s="18" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>28</t>
         </is>
       </c>
       <c r="T46" s="15">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="U46" s="16">
-        <v>2.06</v>
+        <v>-0.54</v>
       </c>
       <c r="V46" s="15">
-        <v>3290</v>
+        <v>528</v>
       </c>
       <c r="W46" s="15"/>
       <c r="X46" s="15"/>
       <c r="Y46" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z46" s="20">
-        <v>69.99</v>
+        <v>65.99</v>
       </c>
       <c r="AA46"/>
       <c r="AB46"/>
       <c r="AC46" s="15"/>
       <c r="AD46" s="19">
-        <v>171</v>
+        <v>1397</v>
       </c>
       <c r="AE46" s="15">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AF46" s="21">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AG46" s="22">
-        <v>0.1277</v>
+        <v>0</v>
       </c>
       <c r="AH46" s="20">
-        <v>10.6</v>
+        <v>9.1</v>
       </c>
       <c r="AI46" s="16">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="AJ46"/>
       <c r="AK46" s="13" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AL46" s="19">
-        <v>475</v>
+        <v>412</v>
       </c>
       <c r="AM46" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN46" s="13"/>
       <c r="AO46" s="13"/>
       <c r="AP46"/>
       <c r="AQ46" s="19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR46" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS46" s="14" t="inlineStr">
         <is>
-          <t>Lehmann HG</t>
+          <t>Olvy</t>
         </is>
       </c>
       <c r="AT46" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AU46" s="13" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="AV46" s="14" t="inlineStr">
         <is>
-          <t>Greater Poland 63-100 PL</t>
+          <t>NIJMEGEN Gelderland 6511DX NL</t>
         </is>
       </c>
       <c r="AW46" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A7NHEBYLM424G</t>
         </is>
       </c>
       <c r="AX46" s="13"/>
-      <c r="AY46" s="13"/>
+      <c r="AY46" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ46" s="13"/>
       <c r="BA46" s="13"/>
       <c r="BB46" s="13"/>
@@ -17813,46 +17713,50 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD46" s="13"/>
+      <c r="BD46" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE46" s="13"/>
       <c r="BF46" s="13"/>
       <c r="BG46" s="13"/>
       <c r="BH46" s="14"/>
-      <c r="BI46" s="23"/>
+      <c r="BI46" s="23" t="inlineStr">
+        <is>
+          <t>Choix d'Amazon</t>
+        </is>
+      </c>
       <c r="BJ46" s="23" t="inlineStr">
         <is>
-          <t>7,8 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK46" s="23" t="inlineStr">
-        <is>
-          <t>7.80 kg</t>
-        </is>
-      </c>
+          <t>3,5 Kilogrammes</t>
+        </is>
+      </c>
+      <c r="BK46" s="23"/>
       <c r="BL46" s="23" t="inlineStr">
         <is>
-          <t>44P x 36l x 51,5H centimètres</t>
+          <t>30,7P x 28l x 17,1H centimètres</t>
         </is>
       </c>
       <c r="BM46" s="23"/>
       <c r="BN46" s="23" t="inlineStr">
         <is>
-          <t>8.8 kg</t>
+          <t>5.5 kg</t>
         </is>
       </c>
       <c r="BO46" s="23" t="inlineStr">
         <is>
-          <t>8.80 kg</t>
+          <t>5.50 kg</t>
         </is>
       </c>
       <c r="BP46" s="23" t="inlineStr">
         <is>
-          <t>55 x 39.5 x 36 cm</t>
+          <t>43.4 x 33.8 x 26.9 cm</t>
         </is>
       </c>
       <c r="BQ46" s="23" t="inlineStr">
         <is>
-          <t>55.00 x 39.50 x 36.00 cm</t>
+          <t>43.40 x 33.80 x 26.90 cm</t>
         </is>
       </c>
       <c r="BR46" s="13" t="inlineStr">
@@ -17868,206 +17772,104 @@
       <c r="B47" s="13"/>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>B0GNB36YF6</t>
+          <t>B075LJWKCY</t>
         </is>
       </c>
       <c r="D47" s="14"/>
       <c r="E47" s="14"/>
-      <c r="F47" s="14" t="inlineStr">
-        <is>
-          <t>Vonia</t>
-        </is>
-      </c>
+      <c r="F47" s="14"/>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/Lessentielpourvotreint%C3%A9rieur/page/83470C2B-9109-49ED-AB3B-9966C74CD2CC?lp_asin=B0GNB36YF6&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.frundefined</t>
         </is>
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
-          <t>Powell Nettoyeur vapeur 2000 W multi-surfaces avec accessoires, noirsFonctionne à l eau seule sur carrelage, joints, vitres</t>
+          <t>Bissell SpotClean ProsDétachant Portable Spécial Moquette/Tapisserie/Intérieur de Voiture | 750W | Pulvériser, Récurer et A</t>
         </is>
       </c>
       <c r="I47" s="14"/>
       <c r="J47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GNB36YF6?psc=1</t>
+          <t>https://www.amazon.fr/dp/B075LJWKCY?psc=1</t>
         </is>
       </c>
       <c r="K47" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41s1fKip7tL._AC_US600_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71LzhODZgmL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L47" s="14" t="inlineStr">
         <is>
-          <t>B0GNB36YF6</t>
-        </is>
-      </c>
-      <c r="M47" s="14" t="inlineStr">
-        <is>
-          <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Nettoyeurs tapis et moquettes</t>
-        </is>
-      </c>
-      <c r="N47" s="14" t="inlineStr">
-        <is>
-          <t>Voir les 100 premiers en Cuisine et Maison</t>
-        </is>
-      </c>
-      <c r="O47" s="15">
-        <v>70062</v>
-      </c>
-      <c r="P47" s="15">
-        <v>50089</v>
-      </c>
-      <c r="Q47" s="16">
-        <v>0.4</v>
-      </c>
-      <c r="R47" s="17" t="inlineStr">
-        <is>
-          <t>Nettoyeurs tapis et moquettes</t>
-        </is>
-      </c>
-      <c r="S47" s="18" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="T47" s="15">
-        <v>15</v>
-      </c>
+          <t>B075LJWKCY</t>
+        </is>
+      </c>
+      <c r="M47" s="14"/>
+      <c r="N47" s="14"/>
+      <c r="O47" s="15"/>
+      <c r="P47" s="15"/>
+      <c r="Q47" s="16"/>
+      <c r="R47" s="17"/>
+      <c r="S47" s="18"/>
+      <c r="T47" s="15"/>
       <c r="U47" s="16"/>
-      <c r="V47" s="15">
-        <v>937</v>
-      </c>
+      <c r="V47" s="15"/>
       <c r="W47" s="15"/>
       <c r="X47" s="15"/>
-      <c r="Y47" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z47" s="20">
-        <v>62.46</v>
-      </c>
+      <c r="Y47" s="19"/>
+      <c r="Z47" s="20"/>
       <c r="AA47"/>
       <c r="AB47"/>
       <c r="AC47" s="15"/>
       <c r="AD47" s="19">
-        <v>12</v>
-      </c>
-      <c r="AE47" s="15">
-        <v>0</v>
-      </c>
+        <v>12913</v>
+      </c>
+      <c r="AE47" s="15"/>
       <c r="AF47" s="21">
         <v>4.6</v>
       </c>
       <c r="AG47" s="22">
         <v>0</v>
       </c>
-      <c r="AH47" s="20">
-        <v>9.32</v>
-      </c>
+      <c r="AH47" s="20"/>
       <c r="AI47" s="16">
-        <v>0.73</v>
+        <v>0</v>
       </c>
       <c r="AJ47"/>
-      <c r="AK47" s="13" t="inlineStr">
-        <is>
-          <t>2026-02-18</t>
-        </is>
-      </c>
-      <c r="AL47" s="19">
-        <v>232</v>
-      </c>
-      <c r="AM47" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
+      <c r="AK47" s="13"/>
+      <c r="AL47" s="19"/>
+      <c r="AM47" s="13"/>
       <c r="AN47" s="13"/>
       <c r="AO47" s="13"/>
       <c r="AP47"/>
       <c r="AQ47" s="19"/>
-      <c r="AR47" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS47" s="14" t="inlineStr">
-        <is>
-          <t>Dennepark B.V</t>
-        </is>
-      </c>
-      <c r="AT47" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU47" s="13" t="inlineStr">
-        <is>
-          <t>NL</t>
-        </is>
-      </c>
-      <c r="AV47" s="14" t="inlineStr">
-        <is>
-          <t>Zuid-Holland 2497 GC NL</t>
-        </is>
-      </c>
-      <c r="AW47" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A25QV76UBVZPI4</t>
-        </is>
-      </c>
+      <c r="AR47" s="19"/>
+      <c r="AS47" s="14"/>
+      <c r="AT47" s="13"/>
+      <c r="AU47" s="13"/>
+      <c r="AV47" s="14"/>
+      <c r="AW47" s="13"/>
       <c r="AX47" s="13"/>
       <c r="AY47" s="13"/>
       <c r="AZ47" s="13"/>
       <c r="BA47" s="13"/>
       <c r="BB47" s="13"/>
       <c r="BC47" s="13"/>
-      <c r="BD47" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD47" s="13"/>
       <c r="BE47" s="13"/>
       <c r="BF47" s="13"/>
       <c r="BG47" s="13"/>
       <c r="BH47" s="14"/>
       <c r="BI47" s="23"/>
-      <c r="BJ47" s="23" t="inlineStr">
-        <is>
-          <t>3,6 Kilogrammes</t>
-        </is>
-      </c>
+      <c r="BJ47" s="23"/>
       <c r="BK47" s="23"/>
-      <c r="BL47" s="23" t="inlineStr">
-        <is>
-          <t>37P x 26,5l x 24H centimètres</t>
-        </is>
-      </c>
+      <c r="BL47" s="23"/>
       <c r="BM47" s="23"/>
-      <c r="BN47" s="23" t="inlineStr">
-        <is>
-          <t>3.6 kg</t>
-        </is>
-      </c>
-      <c r="BO47" s="23" t="inlineStr">
-        <is>
-          <t>3.60 kg</t>
-        </is>
-      </c>
-      <c r="BP47" s="23" t="inlineStr">
-        <is>
-          <t>47 x 33.5 x 31.2 cm</t>
-        </is>
-      </c>
-      <c r="BQ47" s="23" t="inlineStr">
-        <is>
-          <t>47.00 x 33.50 x 31.20 cm</t>
-        </is>
-      </c>
-      <c r="BR47" s="13" t="inlineStr">
-        <is>
-          <t>轻型标准大件</t>
-        </is>
-      </c>
+      <c r="BN47" s="23"/>
+      <c r="BO47" s="23"/>
+      <c r="BP47" s="23"/>
+      <c r="BQ47" s="23"/>
+      <c r="BR47" s="13"/>
     </row>
     <row r="48" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="13">
@@ -18076,222 +17878,106 @@
       <c r="B48" s="13"/>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>B0FMG1PY3G</t>
+          <t>B0FXX9KJ1D</t>
         </is>
       </c>
       <c r="D48" s="14"/>
       <c r="E48" s="14"/>
-      <c r="F48" s="14" t="inlineStr">
-        <is>
-          <t>Olvy</t>
-        </is>
-      </c>
+      <c r="F48" s="14"/>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/OLVY/page/0323FB43-67E5-4EBB-83A3-4CA8B62531C9?lp_asin=B0FMG1PY3G&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.frundefined</t>
         </is>
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>Olvy Shampouineuse Canape Nettoyeur Tapis Injecteur Extracteurs1 Appareil | 17000 PA Aspiration Profonde | Tapis &amp; Moquette</t>
+          <t>Polti StainOver Pet SC50, nettoyeur vapeur permettant d'éliminer les tachess2000 W, 4 en 1, détachant avec fonction vapeur,</t>
         </is>
       </c>
       <c r="I48" s="14"/>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0FMG1PY3G?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0FXX9KJ1D?psc=1</t>
         </is>
       </c>
       <c r="K48" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41dgQOFmcHL._AC_US600_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/51QsiPBPCjL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>B0FMG1PY3G</t>
-        </is>
-      </c>
-      <c r="M48" s="14" t="inlineStr">
-        <is>
-          <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Nettoyeurs tapis et moquettes</t>
-        </is>
-      </c>
-      <c r="N48" s="14" t="inlineStr">
-        <is>
-          <t>Voir les 100 premiers en Cuisine et Maison</t>
-        </is>
-      </c>
-      <c r="O48" s="15">
-        <v>15779</v>
-      </c>
-      <c r="P48" s="15">
-        <v>4455</v>
-      </c>
-      <c r="Q48" s="16">
-        <v>0.17</v>
-      </c>
-      <c r="R48" s="17" t="inlineStr">
-        <is>
-          <t>Nettoyeurs tapis et moquettes</t>
-        </is>
-      </c>
-      <c r="S48" s="18" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="T48" s="15">
-        <v>8</v>
-      </c>
-      <c r="U48" s="16">
-        <v>-0.54</v>
-      </c>
-      <c r="V48" s="15">
-        <v>528</v>
-      </c>
+          <t>B0FXX9KJ1D</t>
+        </is>
+      </c>
+      <c r="M48" s="14"/>
+      <c r="N48" s="14"/>
+      <c r="O48" s="15"/>
+      <c r="P48" s="15"/>
+      <c r="Q48" s="16"/>
+      <c r="R48" s="17"/>
+      <c r="S48" s="18"/>
+      <c r="T48" s="15"/>
+      <c r="U48" s="16"/>
+      <c r="V48" s="15"/>
       <c r="W48" s="15"/>
       <c r="X48" s="15"/>
-      <c r="Y48" s="19">
-        <v>3</v>
-      </c>
+      <c r="Y48" s="19"/>
       <c r="Z48" s="20">
-        <v>65.99</v>
+        <v>274.17</v>
       </c>
       <c r="AA48"/>
       <c r="AB48"/>
       <c r="AC48" s="15"/>
       <c r="AD48" s="19">
-        <v>1397</v>
-      </c>
-      <c r="AE48" s="15">
-        <v>0</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="AE48" s="15"/>
       <c r="AF48" s="21">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AG48" s="22">
         <v>0</v>
       </c>
-      <c r="AH48" s="20">
-        <v>9.1</v>
-      </c>
+      <c r="AH48" s="20"/>
       <c r="AI48" s="16">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="AJ48"/>
-      <c r="AK48" s="13" t="inlineStr">
-        <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AL48" s="19">
-        <v>412</v>
-      </c>
-      <c r="AM48" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
+      <c r="AK48" s="13"/>
+      <c r="AL48" s="19"/>
+      <c r="AM48" s="13"/>
       <c r="AN48" s="13"/>
       <c r="AO48" s="13"/>
       <c r="AP48"/>
-      <c r="AQ48" s="19">
-        <v>10</v>
-      </c>
-      <c r="AR48" s="19">
-        <v>2</v>
-      </c>
-      <c r="AS48" s="14" t="inlineStr">
-        <is>
-          <t>Olvy</t>
-        </is>
-      </c>
-      <c r="AT48" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU48" s="13" t="inlineStr">
-        <is>
-          <t>NL</t>
-        </is>
-      </c>
-      <c r="AV48" s="14" t="inlineStr">
-        <is>
-          <t>NIJMEGEN Gelderland 6511DX NL</t>
-        </is>
-      </c>
-      <c r="AW48" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A7NHEBYLM424G</t>
-        </is>
-      </c>
+      <c r="AQ48" s="19"/>
+      <c r="AR48" s="19"/>
+      <c r="AS48" s="14"/>
+      <c r="AT48" s="13"/>
+      <c r="AU48" s="13"/>
+      <c r="AV48" s="14"/>
+      <c r="AW48" s="13"/>
       <c r="AX48" s="13"/>
-      <c r="AY48" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY48" s="13"/>
       <c r="AZ48" s="13"/>
       <c r="BA48" s="13"/>
       <c r="BB48" s="13"/>
-      <c r="BC48" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD48" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC48" s="13"/>
+      <c r="BD48" s="13"/>
       <c r="BE48" s="13"/>
       <c r="BF48" s="13"/>
       <c r="BG48" s="13"/>
       <c r="BH48" s="14"/>
-      <c r="BI48" s="23" t="inlineStr">
-        <is>
-          <t>Choix d'Amazon</t>
-        </is>
-      </c>
-      <c r="BJ48" s="23" t="inlineStr">
-        <is>
-          <t>3,5 Kilogrammes</t>
-        </is>
-      </c>
+      <c r="BI48" s="23"/>
+      <c r="BJ48" s="23"/>
       <c r="BK48" s="23"/>
-      <c r="BL48" s="23" t="inlineStr">
-        <is>
-          <t>30,7P x 28l x 17,1H centimètres</t>
-        </is>
-      </c>
+      <c r="BL48" s="23"/>
       <c r="BM48" s="23"/>
-      <c r="BN48" s="23" t="inlineStr">
-        <is>
-          <t>5.5 kg</t>
-        </is>
-      </c>
-      <c r="BO48" s="23" t="inlineStr">
-        <is>
-          <t>5.50 kg</t>
-        </is>
-      </c>
-      <c r="BP48" s="23" t="inlineStr">
-        <is>
-          <t>43.4 x 33.8 x 26.9 cm</t>
-        </is>
-      </c>
-      <c r="BQ48" s="23" t="inlineStr">
-        <is>
-          <t>43.40 x 33.80 x 26.90 cm</t>
-        </is>
-      </c>
-      <c r="BR48" s="13" t="inlineStr">
-        <is>
-          <t>轻型标准大件</t>
-        </is>
-      </c>
+      <c r="BN48" s="23"/>
+      <c r="BO48" s="23"/>
+      <c r="BP48" s="23"/>
+      <c r="BQ48" s="23"/>
+      <c r="BR48" s="13"/>
     </row>
     <row r="49" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="13">
@@ -18300,7 +17986,7 @@
       <c r="B49" s="13"/>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>B075LJWKCY</t>
+          <t>B0HFJJMHF6</t>
         </is>
       </c>
       <c r="D49" s="14"/>
@@ -18313,23 +17999,23 @@
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
-          <t>Bissell SpotClean ProsDétachant Portable Spécial Moquette/Tapisserie/Intérieur de Voiture | 750W | Pulvériser, Récurer et A</t>
+          <t>STARRYBOT Nettoyeur Vapeur Canapé Portable 22kPa, Shampouineuse GrissChauffage intégré pour taches d’animaux, tapis, escali</t>
         </is>
       </c>
       <c r="I49" s="14"/>
       <c r="J49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B075LJWKCY?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0HFJJMHF6?psc=1</t>
         </is>
       </c>
       <c r="K49" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71LzhODZgmL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/41Q88WnGsRL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L49" s="14" t="inlineStr">
         <is>
-          <t>B075LJWKCY</t>
+          <t>B0HFJJMHF6</t>
         </is>
       </c>
       <c r="M49" s="14"/>
@@ -18350,11 +18036,11 @@
       <c r="AB49"/>
       <c r="AC49" s="15"/>
       <c r="AD49" s="19">
-        <v>12913</v>
+        <v>315</v>
       </c>
       <c r="AE49" s="15"/>
       <c r="AF49" s="21">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AG49" s="22">
         <v>0</v>
@@ -18398,220 +18084,6 @@
       <c r="BP49" s="23"/>
       <c r="BQ49" s="23"/>
       <c r="BR49" s="13"/>
-    </row>
-    <row r="50" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="13">
-        <v>49</v>
-      </c>
-      <c r="B50" s="13"/>
-      <c r="C50" s="14" t="inlineStr">
-        <is>
-          <t>B0FXX9KJ1D</t>
-        </is>
-      </c>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.frundefined</t>
-        </is>
-      </c>
-      <c r="H50" s="14" t="inlineStr">
-        <is>
-          <t>Polti StainOver Pet SC50, nettoyeur vapeur permettant d'éliminer les tachess2000 W, 4 en 1, détachant avec fonction vapeur,</t>
-        </is>
-      </c>
-      <c r="I50" s="14"/>
-      <c r="J50" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/dp/B0FXX9KJ1D?psc=1</t>
-        </is>
-      </c>
-      <c r="K50" s="14" t="inlineStr">
-        <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/51QsiPBPCjL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L50" s="14" t="inlineStr">
-        <is>
-          <t>B0FXX9KJ1D</t>
-        </is>
-      </c>
-      <c r="M50" s="14"/>
-      <c r="N50" s="14"/>
-      <c r="O50" s="15"/>
-      <c r="P50" s="15"/>
-      <c r="Q50" s="16"/>
-      <c r="R50" s="17"/>
-      <c r="S50" s="18"/>
-      <c r="T50" s="15"/>
-      <c r="U50" s="16"/>
-      <c r="V50" s="15"/>
-      <c r="W50" s="15"/>
-      <c r="X50" s="15"/>
-      <c r="Y50" s="19"/>
-      <c r="Z50" s="20">
-        <v>274.17</v>
-      </c>
-      <c r="AA50"/>
-      <c r="AB50"/>
-      <c r="AC50" s="15"/>
-      <c r="AD50" s="19">
-        <v>17</v>
-      </c>
-      <c r="AE50" s="15"/>
-      <c r="AF50" s="21">
-        <v>3.9</v>
-      </c>
-      <c r="AG50" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH50" s="20"/>
-      <c r="AI50" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ50"/>
-      <c r="AK50" s="13"/>
-      <c r="AL50" s="19"/>
-      <c r="AM50" s="13"/>
-      <c r="AN50" s="13"/>
-      <c r="AO50" s="13"/>
-      <c r="AP50"/>
-      <c r="AQ50" s="19"/>
-      <c r="AR50" s="19"/>
-      <c r="AS50" s="14"/>
-      <c r="AT50" s="13"/>
-      <c r="AU50" s="13"/>
-      <c r="AV50" s="14"/>
-      <c r="AW50" s="13"/>
-      <c r="AX50" s="13"/>
-      <c r="AY50" s="13"/>
-      <c r="AZ50" s="13"/>
-      <c r="BA50" s="13"/>
-      <c r="BB50" s="13"/>
-      <c r="BC50" s="13"/>
-      <c r="BD50" s="13"/>
-      <c r="BE50" s="13"/>
-      <c r="BF50" s="13"/>
-      <c r="BG50" s="13"/>
-      <c r="BH50" s="14"/>
-      <c r="BI50" s="23"/>
-      <c r="BJ50" s="23"/>
-      <c r="BK50" s="23"/>
-      <c r="BL50" s="23"/>
-      <c r="BM50" s="23"/>
-      <c r="BN50" s="23"/>
-      <c r="BO50" s="23"/>
-      <c r="BP50" s="23"/>
-      <c r="BQ50" s="23"/>
-      <c r="BR50" s="13"/>
-    </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="13">
-        <v>50</v>
-      </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="14" t="inlineStr">
-        <is>
-          <t>B0HFJJMHF6</t>
-        </is>
-      </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.frundefined</t>
-        </is>
-      </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>STARRYBOT Nettoyeur Vapeur Canapé Portable 22kPa, Shampouineuse GrissChauffage intégré pour taches d’animaux, tapis, escali</t>
-        </is>
-      </c>
-      <c r="I51" s="14"/>
-      <c r="J51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/dp/B0HFJJMHF6?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="14" t="inlineStr">
-        <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/41Q88WnGsRL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="14" t="inlineStr">
-        <is>
-          <t>B0HFJJMHF6</t>
-        </is>
-      </c>
-      <c r="M51" s="14"/>
-      <c r="N51" s="14"/>
-      <c r="O51" s="15"/>
-      <c r="P51" s="15"/>
-      <c r="Q51" s="16"/>
-      <c r="R51" s="17"/>
-      <c r="S51" s="18"/>
-      <c r="T51" s="15"/>
-      <c r="U51" s="16"/>
-      <c r="V51" s="15"/>
-      <c r="W51" s="15"/>
-      <c r="X51" s="15"/>
-      <c r="Y51" s="19"/>
-      <c r="Z51" s="20"/>
-      <c r="AA51"/>
-      <c r="AB51"/>
-      <c r="AC51" s="15"/>
-      <c r="AD51" s="19">
-        <v>315</v>
-      </c>
-      <c r="AE51" s="15"/>
-      <c r="AF51" s="21">
-        <v>4.7</v>
-      </c>
-      <c r="AG51" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH51" s="20"/>
-      <c r="AI51" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="13"/>
-      <c r="AL51" s="19"/>
-      <c r="AM51" s="13"/>
-      <c r="AN51" s="13"/>
-      <c r="AO51" s="13"/>
-      <c r="AP51"/>
-      <c r="AQ51" s="19"/>
-      <c r="AR51" s="19"/>
-      <c r="AS51" s="14"/>
-      <c r="AT51" s="13"/>
-      <c r="AU51" s="13"/>
-      <c r="AV51" s="14"/>
-      <c r="AW51" s="13"/>
-      <c r="AX51" s="13"/>
-      <c r="AY51" s="13"/>
-      <c r="AZ51" s="13"/>
-      <c r="BA51" s="13"/>
-      <c r="BB51" s="13"/>
-      <c r="BC51" s="13"/>
-      <c r="BD51" s="13"/>
-      <c r="BE51" s="13"/>
-      <c r="BF51" s="13"/>
-      <c r="BG51" s="13"/>
-      <c r="BH51" s="14"/>
-      <c r="BI51" s="23"/>
-      <c r="BJ51" s="23"/>
-      <c r="BK51" s="23"/>
-      <c r="BL51" s="23"/>
-      <c r="BM51" s="23"/>
-      <c r="BN51" s="23"/>
-      <c r="BO51" s="23"/>
-      <c r="BP51" s="23"/>
-      <c r="BQ51" s="23"/>
-      <c r="BR51" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18842,153 +18314,138 @@
     <hyperlink ref="M32" r:id="rId223" tooltip="https://www.amazon.fr/b?node=3575198031"/>
     <hyperlink ref="N32" r:id="rId224"/>
     <hyperlink ref="AW32" r:id="rId225" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A190HADBP97HLJ"/>
-    <hyperlink ref="C33" r:id="rId226" tooltip="https://www.amazon.fr/dp/B07999DC2C"/>
-    <hyperlink ref="G33" r:id="rId227" tooltip="https://www.amazon.fr/stores/BISSELL/page/257B1210-BA3F-4555-82AC-76498F62C992?lp_asin=B07999DC2C&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J33" r:id="rId228" tooltip="https://www.amazon.fr/dp/B07999DC2C?psc=1"/>
-    <hyperlink ref="K33" r:id="rId229" tooltip="https://m.media-amazon.com/images/I/41iS9PbnYAL._AC_US600_.jpg"/>
-    <hyperlink ref="L33" r:id="rId230" tooltip="https://www.amazon.fr/dp/B07999DC2C"/>
-    <hyperlink ref="M33" r:id="rId231" tooltip="https://www.amazon.fr/b?node=3575197031"/>
+    <hyperlink ref="C33" r:id="rId226" tooltip="https://www.amazon.fr/dp/B0C3VKT151"/>
+    <hyperlink ref="G33" r:id="rId227" tooltip="https://www.amazon.fr/SUPER-CLEAN/b/ref=bl_dp_s_web_56519001031?ie=UTF8&amp;node=56519001031&amp;field-lbr_brands_browse-bin=SUPER+CLEAN"/>
+    <hyperlink ref="J33" r:id="rId228" tooltip="https://www.amazon.fr/dp/B0C3VKT151?psc=1"/>
+    <hyperlink ref="K33" r:id="rId229" tooltip="https://images-na.ssl-images-amazon.com/images/I/51BtUWuNe6L._AC_US600_.jpg"/>
+    <hyperlink ref="L33" r:id="rId230" tooltip="https://www.amazon.fr/dp/B0C3VKT151"/>
+    <hyperlink ref="M33" r:id="rId231" tooltip="https://www.amazon.fr/b?node=3575161031"/>
     <hyperlink ref="N33" r:id="rId232"/>
-    <hyperlink ref="C34" r:id="rId233" tooltip="https://www.amazon.fr/dp/B0C3VKT151"/>
-    <hyperlink ref="G34" r:id="rId234" tooltip="https://www.amazon.fr/SUPER-CLEAN/b/ref=bl_dp_s_web_56519001031?ie=UTF8&amp;node=56519001031&amp;field-lbr_brands_browse-bin=SUPER+CLEAN"/>
-    <hyperlink ref="J34" r:id="rId235" tooltip="https://www.amazon.fr/dp/B0C3VKT151?psc=1"/>
-    <hyperlink ref="K34" r:id="rId236" tooltip="https://images-na.ssl-images-amazon.com/images/I/51BtUWuNe6L._AC_US600_.jpg"/>
-    <hyperlink ref="L34" r:id="rId237" tooltip="https://www.amazon.fr/dp/B0C3VKT151"/>
-    <hyperlink ref="M34" r:id="rId238" tooltip="https://www.amazon.fr/b?node=3575161031"/>
-    <hyperlink ref="N34" r:id="rId239"/>
-    <hyperlink ref="AW34" r:id="rId240" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3H8GAVD67YD0F"/>
-    <hyperlink ref="C35" r:id="rId241" tooltip="https://www.amazon.fr/dp/B0H3LCDNGF"/>
-    <hyperlink ref="G35" r:id="rId242" tooltip="https://www.amazon.fr/stores/LEHMANN/page/EAB8CEA1-93E8-4C19-BC95-67B7BFD404B9?lp_asin=B0H3LCDNGF&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J35" r:id="rId243" tooltip="https://www.amazon.fr/dp/B0H3LCDNGF?psc=1"/>
-    <hyperlink ref="K35" r:id="rId244" tooltip="https://m.media-amazon.com/images/I/41Md9nniqDL._AC_US600_.jpg"/>
-    <hyperlink ref="L35" r:id="rId245" tooltip="https://www.amazon.fr/dp/B0H3LCDNGF"/>
-    <hyperlink ref="M35" r:id="rId246" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N35" r:id="rId247"/>
-    <hyperlink ref="AW35" r:id="rId248" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH"/>
-    <hyperlink ref="C36" r:id="rId249" tooltip="https://www.amazon.fr/dp/B0GQJ6RWKR"/>
-    <hyperlink ref="G36" r:id="rId250" tooltip="https://www.amazon.fr/stores/SharkINinja/page/AE46A729-E57D-49FA-B00E-8125E3841DDD?lp_asin=B0GQJ6RWKR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J36" r:id="rId251" tooltip="https://www.amazon.fr/dp/B0GQJ6RWKR?psc=1"/>
-    <hyperlink ref="K36" r:id="rId252" tooltip="https://m.media-amazon.com/images/I/410s8YmSZGL._AC_US600_.jpg"/>
-    <hyperlink ref="L36" r:id="rId253" tooltip="https://www.amazon.fr/dp/B0GQJ6RWKR"/>
+    <hyperlink ref="AW33" r:id="rId233" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3H8GAVD67YD0F"/>
+    <hyperlink ref="C34" r:id="rId234" tooltip="https://www.amazon.fr/dp/B0H3LCDNGF"/>
+    <hyperlink ref="G34" r:id="rId235" tooltip="https://www.amazon.fr/stores/LEHMANN/page/EAB8CEA1-93E8-4C19-BC95-67B7BFD404B9?lp_asin=B0H3LCDNGF&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J34" r:id="rId236" tooltip="https://www.amazon.fr/dp/B0H3LCDNGF?psc=1"/>
+    <hyperlink ref="K34" r:id="rId237" tooltip="https://m.media-amazon.com/images/I/41Md9nniqDL._AC_US600_.jpg"/>
+    <hyperlink ref="L34" r:id="rId238" tooltip="https://www.amazon.fr/dp/B0H3LCDNGF"/>
+    <hyperlink ref="M34" r:id="rId239" tooltip="https://www.amazon.fr/b?node=3575198031"/>
+    <hyperlink ref="N34" r:id="rId240"/>
+    <hyperlink ref="AW34" r:id="rId241" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH"/>
+    <hyperlink ref="C35" r:id="rId242" tooltip="https://www.amazon.fr/dp/B0GQJ6RWKR"/>
+    <hyperlink ref="G35" r:id="rId243" tooltip="https://www.amazon.fr/stores/SharkINinja/page/AE46A729-E57D-49FA-B00E-8125E3841DDD?lp_asin=B0GQJ6RWKR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J35" r:id="rId244" tooltip="https://www.amazon.fr/dp/B0GQJ6RWKR?psc=1"/>
+    <hyperlink ref="K35" r:id="rId245" tooltip="https://m.media-amazon.com/images/I/410s8YmSZGL._AC_US600_.jpg"/>
+    <hyperlink ref="L35" r:id="rId246" tooltip="https://www.amazon.fr/dp/B0GQJ6RWKR"/>
+    <hyperlink ref="M35" r:id="rId247" tooltip="https://www.amazon.fr/b?node=3575198031"/>
+    <hyperlink ref="N35" r:id="rId248"/>
+    <hyperlink ref="C36" r:id="rId249" tooltip="https://www.amazon.fr/dp/B0FS2B5W6P"/>
+    <hyperlink ref="G36" r:id="rId250" tooltip="https://www.amazon.fr/stores/LEHMANN/page/EAB8CEA1-93E8-4C19-BC95-67B7BFD404B9?lp_asin=B0FS2B5W6P&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J36" r:id="rId251" tooltip="https://www.amazon.fr/dp/B0FS2B5W6P?psc=1"/>
+    <hyperlink ref="K36" r:id="rId252" tooltip="https://images-na.ssl-images-amazon.com/images/I/71LqABaCHVL._AC_US600_.jpg"/>
+    <hyperlink ref="L36" r:id="rId253" tooltip="https://www.amazon.fr/dp/B0FS2B5W6P"/>
     <hyperlink ref="M36" r:id="rId254" tooltip="https://www.amazon.fr/b?node=3575198031"/>
     <hyperlink ref="N36" r:id="rId255"/>
-    <hyperlink ref="C37" r:id="rId256" tooltip="https://www.amazon.fr/dp/B0FS2B5W6P"/>
-    <hyperlink ref="G37" r:id="rId257" tooltip="https://www.amazon.fr/stores/LEHMANN/page/EAB8CEA1-93E8-4C19-BC95-67B7BFD404B9?lp_asin=B0FS2B5W6P&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J37" r:id="rId258" tooltip="https://www.amazon.fr/dp/B0FS2B5W6P?psc=1"/>
-    <hyperlink ref="K37" r:id="rId259" tooltip="https://images-na.ssl-images-amazon.com/images/I/71LqABaCHVL._AC_US600_.jpg"/>
-    <hyperlink ref="L37" r:id="rId260" tooltip="https://www.amazon.fr/dp/B0FS2B5W6P"/>
-    <hyperlink ref="M37" r:id="rId261" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N37" r:id="rId262"/>
-    <hyperlink ref="AW37" r:id="rId263" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH"/>
-    <hyperlink ref="C38" r:id="rId264" tooltip="https://www.amazon.fr/dp/B0CVXJ1VHT"/>
-    <hyperlink ref="G38" r:id="rId265" tooltip="https://www.amazon.fr/stores/BISSELL/page/257B1210-BA3F-4555-82AC-76498F62C992?lp_asin=B0CVXJ1VHT&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J38" r:id="rId266" tooltip="https://www.amazon.fr/dp/B0CVXJ1VHT?psc=1"/>
-    <hyperlink ref="K38" r:id="rId267" tooltip="https://m.media-amazon.com/images/I/31jphvfzkmL._AC_US600_.jpg"/>
-    <hyperlink ref="L38" r:id="rId268" tooltip="https://www.amazon.fr/dp/B0CVXJ1VHT"/>
+    <hyperlink ref="AW36" r:id="rId256" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH"/>
+    <hyperlink ref="C37" r:id="rId257" tooltip="https://www.amazon.fr/dp/B0CVXJ1VHT"/>
+    <hyperlink ref="G37" r:id="rId258" tooltip="https://www.amazon.fr/stores/BISSELL/page/257B1210-BA3F-4555-82AC-76498F62C992?lp_asin=B0CVXJ1VHT&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J37" r:id="rId259" tooltip="https://www.amazon.fr/dp/B0CVXJ1VHT?psc=1"/>
+    <hyperlink ref="K37" r:id="rId260" tooltip="https://m.media-amazon.com/images/I/31jphvfzkmL._AC_US600_.jpg"/>
+    <hyperlink ref="L37" r:id="rId261" tooltip="https://www.amazon.fr/dp/B0CVXJ1VHT"/>
+    <hyperlink ref="M37" r:id="rId262" tooltip="https://www.amazon.fr/b?node=3575198031"/>
+    <hyperlink ref="N37" r:id="rId263"/>
+    <hyperlink ref="C38" r:id="rId264" tooltip="https://www.amazon.fr/dp/B01HZUX61M"/>
+    <hyperlink ref="G38" r:id="rId265" tooltip="https://www.amazon.fr/stores/Technfast/page/5C561153-C96A-4DCF-BA10-143B211F8707?lp_asin=B01HZUX61M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J38" r:id="rId266" tooltip="https://www.amazon.fr/dp/B01HZUX61M?psc=1"/>
+    <hyperlink ref="K38" r:id="rId267" tooltip="https://m.media-amazon.com/images/I/319Ry9yZeTL._AC_US600_.jpg"/>
+    <hyperlink ref="L38" r:id="rId268" tooltip="https://www.amazon.fr/dp/B01HZUX61M"/>
     <hyperlink ref="M38" r:id="rId269" tooltip="https://www.amazon.fr/b?node=3575198031"/>
     <hyperlink ref="N38" r:id="rId270"/>
-    <hyperlink ref="C39" r:id="rId271" tooltip="https://www.amazon.fr/dp/B01HZUX61M"/>
-    <hyperlink ref="G39" r:id="rId272" tooltip="https://www.amazon.fr/stores/Technfast/page/5C561153-C96A-4DCF-BA10-143B211F8707?lp_asin=B01HZUX61M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J39" r:id="rId273" tooltip="https://www.amazon.fr/dp/B01HZUX61M?psc=1"/>
-    <hyperlink ref="K39" r:id="rId274" tooltip="https://m.media-amazon.com/images/I/319Ry9yZeTL._AC_US600_.jpg"/>
-    <hyperlink ref="L39" r:id="rId275" tooltip="https://www.amazon.fr/dp/B01HZUX61M"/>
-    <hyperlink ref="M39" r:id="rId276" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N39" r:id="rId277"/>
-    <hyperlink ref="AW39" r:id="rId278" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AMPFK1KKUPHEA"/>
-    <hyperlink ref="C40" r:id="rId279" tooltip="https://www.amazon.fr/dp/B0FFHS6LWS"/>
-    <hyperlink ref="G40" r:id="rId280" tooltip="https://www.amazon.fr/stores/OLVY/page/0323FB43-67E5-4EBB-83A3-4CA8B62531C9?lp_asin=B0FFHS6LWS&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J40" r:id="rId281" tooltip="https://www.amazon.fr/dp/B0FFHS6LWS?psc=1"/>
-    <hyperlink ref="K40" r:id="rId282" tooltip="https://m.media-amazon.com/images/I/41GxuZ621XL._AC_US600_.jpg"/>
-    <hyperlink ref="L40" r:id="rId283" tooltip="https://www.amazon.fr/dp/B0FFHS6LWS"/>
-    <hyperlink ref="M40" r:id="rId284" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N40" r:id="rId285"/>
-    <hyperlink ref="AW40" r:id="rId286" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A7NHEBYLM424G"/>
-    <hyperlink ref="C41" r:id="rId287" tooltip="https://www.amazon.fr/dp/B0CLYF3DMZ"/>
-    <hyperlink ref="G41" r:id="rId288" tooltip="https://www.amazon.fr/stores/LEHMANN/page/EAB8CEA1-93E8-4C19-BC95-67B7BFD404B9?lp_asin=B0CLYF3DMZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J41" r:id="rId289" tooltip="https://www.amazon.fr/dp/B0CLYF3DMZ?psc=1"/>
-    <hyperlink ref="K41" r:id="rId290" tooltip="https://m.media-amazon.com/images/I/41R8Ql2gj9L._AC_US600_.jpg"/>
-    <hyperlink ref="L41" r:id="rId291" tooltip="https://www.amazon.fr/dp/B0CLYF3DMZ"/>
-    <hyperlink ref="M41" r:id="rId292" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N41" r:id="rId293"/>
-    <hyperlink ref="AW41" r:id="rId294" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH"/>
-    <hyperlink ref="C42" r:id="rId295" tooltip="https://www.amazon.fr/dp/B0B3J3Q9RD"/>
-    <hyperlink ref="G42" r:id="rId296" tooltip="https://www.amazon.fr/stores/HAUSHOF/page/F29AB38F-2156-4E8D-8FE4-F22692B62A19?lp_asin=B0B3J3Q9RD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J42" r:id="rId297" tooltip="https://www.amazon.fr/dp/B0B3J3Q9RD?psc=1"/>
-    <hyperlink ref="K42" r:id="rId298" tooltip="https://images-na.ssl-images-amazon.com/images/I/71xJpcYtPpL._AC_US600_.jpg"/>
-    <hyperlink ref="L42" r:id="rId299" tooltip="https://www.amazon.fr/dp/B0B3J3Q9RD"/>
+    <hyperlink ref="AW38" r:id="rId271" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AMPFK1KKUPHEA"/>
+    <hyperlink ref="C39" r:id="rId272" tooltip="https://www.amazon.fr/dp/B0FFHS6LWS"/>
+    <hyperlink ref="G39" r:id="rId273" tooltip="https://www.amazon.fr/stores/OLVY/page/0323FB43-67E5-4EBB-83A3-4CA8B62531C9?lp_asin=B0FFHS6LWS&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J39" r:id="rId274" tooltip="https://www.amazon.fr/dp/B0FFHS6LWS?psc=1"/>
+    <hyperlink ref="K39" r:id="rId275" tooltip="https://m.media-amazon.com/images/I/41GxuZ621XL._AC_US600_.jpg"/>
+    <hyperlink ref="L39" r:id="rId276" tooltip="https://www.amazon.fr/dp/B0FFHS6LWS"/>
+    <hyperlink ref="M39" r:id="rId277" tooltip="https://www.amazon.fr/b?node=3575198031"/>
+    <hyperlink ref="N39" r:id="rId278"/>
+    <hyperlink ref="AW39" r:id="rId279" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A7NHEBYLM424G"/>
+    <hyperlink ref="C40" r:id="rId280" tooltip="https://www.amazon.fr/dp/B0CLYF3DMZ"/>
+    <hyperlink ref="G40" r:id="rId281" tooltip="https://www.amazon.fr/stores/LEHMANN/page/EAB8CEA1-93E8-4C19-BC95-67B7BFD404B9?lp_asin=B0CLYF3DMZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J40" r:id="rId282" tooltip="https://www.amazon.fr/dp/B0CLYF3DMZ?psc=1"/>
+    <hyperlink ref="K40" r:id="rId283" tooltip="https://m.media-amazon.com/images/I/41R8Ql2gj9L._AC_US600_.jpg"/>
+    <hyperlink ref="L40" r:id="rId284" tooltip="https://www.amazon.fr/dp/B0CLYF3DMZ"/>
+    <hyperlink ref="M40" r:id="rId285" tooltip="https://www.amazon.fr/b?node=3575198031"/>
+    <hyperlink ref="N40" r:id="rId286"/>
+    <hyperlink ref="AW40" r:id="rId287" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH"/>
+    <hyperlink ref="C41" r:id="rId288" tooltip="https://www.amazon.fr/dp/B0B3J3Q9RD"/>
+    <hyperlink ref="G41" r:id="rId289" tooltip="https://www.amazon.fr/stores/HAUSHOF/page/F29AB38F-2156-4E8D-8FE4-F22692B62A19?lp_asin=B0B3J3Q9RD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J41" r:id="rId290" tooltip="https://www.amazon.fr/dp/B0B3J3Q9RD?psc=1"/>
+    <hyperlink ref="K41" r:id="rId291" tooltip="https://images-na.ssl-images-amazon.com/images/I/71xJpcYtPpL._AC_US600_.jpg"/>
+    <hyperlink ref="L41" r:id="rId292" tooltip="https://www.amazon.fr/dp/B0B3J3Q9RD"/>
+    <hyperlink ref="M41" r:id="rId293" tooltip="https://www.amazon.fr/b?node=3575198031"/>
+    <hyperlink ref="N41" r:id="rId294"/>
+    <hyperlink ref="C42" r:id="rId295" tooltip="https://www.amazon.fr/dp/B0HFW8M5VH"/>
+    <hyperlink ref="G42" r:id="rId296" tooltip="https://www.amazon.fr/stores/uwant/page/22E764CF-7C20-4A56-AAA4-4DCFB8ECAC57?lp_asin=B0HFW8M5VH&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J42" r:id="rId297" tooltip="https://www.amazon.fr/dp/B0HFW8M5VH?psc=1"/>
+    <hyperlink ref="K42" r:id="rId298" tooltip="https://m.media-amazon.com/images/I/411+BeEHvHL._AC_US600_.jpg"/>
+    <hyperlink ref="L42" r:id="rId299" tooltip="https://www.amazon.fr/dp/B0HFW8M5VH"/>
     <hyperlink ref="M42" r:id="rId300" tooltip="https://www.amazon.fr/b?node=3575198031"/>
     <hyperlink ref="N42" r:id="rId301"/>
-    <hyperlink ref="C43" r:id="rId302" tooltip="https://www.amazon.fr/dp/B0HFW8M5VH"/>
-    <hyperlink ref="G43" r:id="rId303" tooltip="https://www.amazon.fr/stores/uwant/page/22E764CF-7C20-4A56-AAA4-4DCFB8ECAC57?lp_asin=B0HFW8M5VH&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J43" r:id="rId304" tooltip="https://www.amazon.fr/dp/B0HFW8M5VH?psc=1"/>
-    <hyperlink ref="K43" r:id="rId305" tooltip="https://m.media-amazon.com/images/I/411+BeEHvHL._AC_US600_.jpg"/>
-    <hyperlink ref="L43" r:id="rId306" tooltip="https://www.amazon.fr/dp/B0HFW8M5VH"/>
-    <hyperlink ref="M43" r:id="rId307" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N43" r:id="rId308"/>
-    <hyperlink ref="AW43" r:id="rId309" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AR2TXP04XQ1UK"/>
-    <hyperlink ref="C44" r:id="rId310" tooltip="https://www.amazon.fr/dp/B0FH4QL9GN"/>
-    <hyperlink ref="G44" r:id="rId311" tooltip="https://www.amazon.fr/stores/Livatro/page/291E7715-1BBB-4063-93C4-B0F4B3739CDD?lp_asin=B0FH4QL9GN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J44" r:id="rId312" tooltip="https://www.amazon.fr/dp/B0FH4QL9GN?psc=1"/>
-    <hyperlink ref="K44" r:id="rId313" tooltip="https://m.media-amazon.com/images/I/41OIdOf0WOL._AC_US600_.jpg"/>
-    <hyperlink ref="L44" r:id="rId314" tooltip="https://www.amazon.fr/dp/B0FH4QL9GN"/>
-    <hyperlink ref="M44" r:id="rId315" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N44" r:id="rId316"/>
-    <hyperlink ref="AW44" r:id="rId317" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1GEHAEQGC953B"/>
-    <hyperlink ref="C45" r:id="rId318" tooltip="https://www.amazon.fr/dp/B0BSHCQQ4W"/>
-    <hyperlink ref="G45" r:id="rId319" tooltip="https://www.amazon.fr/stores/HKoenig/page/58E8DB4A-AF96-40E3-AB82-3B5DA9F75657?lp_asin=B0BSHCQQ4W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J45" r:id="rId320" tooltip="https://www.amazon.fr/dp/B0BSHCQQ4W?psc=1"/>
-    <hyperlink ref="K45" r:id="rId321" tooltip="https://images-na.ssl-images-amazon.com/images/I/61W1ckv75YL._AC_US600_.jpg"/>
-    <hyperlink ref="L45" r:id="rId322" tooltip="https://www.amazon.fr/dp/B0BSHCQQ4W"/>
-    <hyperlink ref="M45" r:id="rId323" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N45" r:id="rId324"/>
-    <hyperlink ref="AW45" r:id="rId325" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2J1ZXSJG29176"/>
-    <hyperlink ref="C46" r:id="rId326" tooltip="https://www.amazon.fr/dp/B0FDL5FJ5W"/>
-    <hyperlink ref="G46" r:id="rId327" tooltip="https://www.amazon.fr/stores/LEHMANN/page/EAB8CEA1-93E8-4C19-BC95-67B7BFD404B9?lp_asin=B0FDL5FJ5W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J46" r:id="rId328" tooltip="https://www.amazon.fr/dp/B0FDL5FJ5W?psc=1"/>
-    <hyperlink ref="K46" r:id="rId329" tooltip="https://m.media-amazon.com/images/I/41CKqZHXRBL._AC_US600_.jpg"/>
-    <hyperlink ref="L46" r:id="rId330" tooltip="https://www.amazon.fr/dp/B0FDL5FJ5W"/>
-    <hyperlink ref="M46" r:id="rId331" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N46" r:id="rId332"/>
-    <hyperlink ref="AW46" r:id="rId333" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH"/>
-    <hyperlink ref="C47" r:id="rId334" tooltip="https://www.amazon.fr/dp/B0GNB36YF6"/>
-    <hyperlink ref="G47" r:id="rId335" tooltip="https://www.amazon.fr/stores/Lessentielpourvotreint%C3%A9rieur/page/83470C2B-9109-49ED-AB3B-9966C74CD2CC?lp_asin=B0GNB36YF6&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J47" r:id="rId336" tooltip="https://www.amazon.fr/dp/B0GNB36YF6?psc=1"/>
-    <hyperlink ref="K47" r:id="rId337" tooltip="https://m.media-amazon.com/images/I/41s1fKip7tL._AC_US600_.jpg"/>
-    <hyperlink ref="L47" r:id="rId338" tooltip="https://www.amazon.fr/dp/B0GNB36YF6"/>
-    <hyperlink ref="M47" r:id="rId339" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N47" r:id="rId340"/>
-    <hyperlink ref="AW47" r:id="rId341" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A25QV76UBVZPI4"/>
-    <hyperlink ref="C48" r:id="rId342" tooltip="https://www.amazon.fr/dp/B0FMG1PY3G"/>
-    <hyperlink ref="G48" r:id="rId343" tooltip="https://www.amazon.fr/stores/OLVY/page/0323FB43-67E5-4EBB-83A3-4CA8B62531C9?lp_asin=B0FMG1PY3G&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J48" r:id="rId344" tooltip="https://www.amazon.fr/dp/B0FMG1PY3G?psc=1"/>
-    <hyperlink ref="K48" r:id="rId345" tooltip="https://m.media-amazon.com/images/I/41dgQOFmcHL._AC_US600_.jpg"/>
-    <hyperlink ref="L48" r:id="rId346" tooltip="https://www.amazon.fr/dp/B0FMG1PY3G"/>
-    <hyperlink ref="M48" r:id="rId347" tooltip="https://www.amazon.fr/b?node=3575198031"/>
-    <hyperlink ref="N48" r:id="rId348"/>
-    <hyperlink ref="AW48" r:id="rId349" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A7NHEBYLM424G"/>
-    <hyperlink ref="C49" r:id="rId350" tooltip="https://www.amazon.fr/dp/B075LJWKCY"/>
-    <hyperlink ref="G49" r:id="rId351" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J49" r:id="rId352" tooltip="https://www.amazon.fr/dp/B075LJWKCY?psc=1"/>
-    <hyperlink ref="K49" r:id="rId353" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71LzhODZgmL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L49" r:id="rId354" tooltip="https://www.amazon.fr/dp/B075LJWKCY"/>
-    <hyperlink ref="C50" r:id="rId355" tooltip="https://www.amazon.fr/dp/B0FXX9KJ1D"/>
-    <hyperlink ref="G50" r:id="rId356" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J50" r:id="rId357" tooltip="https://www.amazon.fr/dp/B0FXX9KJ1D?psc=1"/>
-    <hyperlink ref="K50" r:id="rId358" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51QsiPBPCjL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L50" r:id="rId359" tooltip="https://www.amazon.fr/dp/B0FXX9KJ1D"/>
-    <hyperlink ref="C51" r:id="rId360" tooltip="https://www.amazon.fr/dp/B0HFJJMHF6"/>
-    <hyperlink ref="G51" r:id="rId361" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J51" r:id="rId362" tooltip="https://www.amazon.fr/dp/B0HFJJMHF6?psc=1"/>
-    <hyperlink ref="K51" r:id="rId363" tooltip="https://images-eu.ssl-images-amazon.com/images/I/41Q88WnGsRL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L51" r:id="rId364" tooltip="https://www.amazon.fr/dp/B0HFJJMHF6"/>
+    <hyperlink ref="AW42" r:id="rId302" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AR2TXP04XQ1UK"/>
+    <hyperlink ref="C43" r:id="rId303" tooltip="https://www.amazon.fr/dp/B0FH4QL9GN"/>
+    <hyperlink ref="G43" r:id="rId304" tooltip="https://www.amazon.fr/stores/Livatro/page/291E7715-1BBB-4063-93C4-B0F4B3739CDD?lp_asin=B0FH4QL9GN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J43" r:id="rId305" tooltip="https://www.amazon.fr/dp/B0FH4QL9GN?psc=1"/>
+    <hyperlink ref="K43" r:id="rId306" tooltip="https://m.media-amazon.com/images/I/41OIdOf0WOL._AC_US600_.jpg"/>
+    <hyperlink ref="L43" r:id="rId307" tooltip="https://www.amazon.fr/dp/B0FH4QL9GN"/>
+    <hyperlink ref="M43" r:id="rId308" tooltip="https://www.amazon.fr/b?node=3575198031"/>
+    <hyperlink ref="N43" r:id="rId309"/>
+    <hyperlink ref="AW43" r:id="rId310" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1GEHAEQGC953B"/>
+    <hyperlink ref="C44" r:id="rId311" tooltip="https://www.amazon.fr/dp/B0BSHCQQ4W"/>
+    <hyperlink ref="G44" r:id="rId312" tooltip="https://www.amazon.fr/stores/HKoenig/page/58E8DB4A-AF96-40E3-AB82-3B5DA9F75657?lp_asin=B0BSHCQQ4W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J44" r:id="rId313" tooltip="https://www.amazon.fr/dp/B0BSHCQQ4W?psc=1"/>
+    <hyperlink ref="K44" r:id="rId314" tooltip="https://images-na.ssl-images-amazon.com/images/I/61W1ckv75YL._AC_US600_.jpg"/>
+    <hyperlink ref="L44" r:id="rId315" tooltip="https://www.amazon.fr/dp/B0BSHCQQ4W"/>
+    <hyperlink ref="M44" r:id="rId316" tooltip="https://www.amazon.fr/b?node=3575198031"/>
+    <hyperlink ref="N44" r:id="rId317"/>
+    <hyperlink ref="AW44" r:id="rId318" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2J1ZXSJG29176"/>
+    <hyperlink ref="C45" r:id="rId319" tooltip="https://www.amazon.fr/dp/B0FDL5FJ5W"/>
+    <hyperlink ref="G45" r:id="rId320" tooltip="https://www.amazon.fr/stores/LEHMANN/page/EAB8CEA1-93E8-4C19-BC95-67B7BFD404B9?lp_asin=B0FDL5FJ5W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J45" r:id="rId321" tooltip="https://www.amazon.fr/dp/B0FDL5FJ5W?psc=1"/>
+    <hyperlink ref="K45" r:id="rId322" tooltip="https://m.media-amazon.com/images/I/41CKqZHXRBL._AC_US600_.jpg"/>
+    <hyperlink ref="L45" r:id="rId323" tooltip="https://www.amazon.fr/dp/B0FDL5FJ5W"/>
+    <hyperlink ref="M45" r:id="rId324" tooltip="https://www.amazon.fr/b?node=3575198031"/>
+    <hyperlink ref="N45" r:id="rId325"/>
+    <hyperlink ref="AW45" r:id="rId326" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH"/>
+    <hyperlink ref="C46" r:id="rId327" tooltip="https://www.amazon.fr/dp/B0FMG1PY3G"/>
+    <hyperlink ref="G46" r:id="rId328" tooltip="https://www.amazon.fr/stores/OLVY/page/0323FB43-67E5-4EBB-83A3-4CA8B62531C9?lp_asin=B0FMG1PY3G&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J46" r:id="rId329" tooltip="https://www.amazon.fr/dp/B0FMG1PY3G?psc=1"/>
+    <hyperlink ref="K46" r:id="rId330" tooltip="https://m.media-amazon.com/images/I/41dgQOFmcHL._AC_US600_.jpg"/>
+    <hyperlink ref="L46" r:id="rId331" tooltip="https://www.amazon.fr/dp/B0FMG1PY3G"/>
+    <hyperlink ref="M46" r:id="rId332" tooltip="https://www.amazon.fr/b?node=3575198031"/>
+    <hyperlink ref="N46" r:id="rId333"/>
+    <hyperlink ref="AW46" r:id="rId334" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A7NHEBYLM424G"/>
+    <hyperlink ref="C47" r:id="rId335" tooltip="https://www.amazon.fr/dp/B075LJWKCY"/>
+    <hyperlink ref="G47" r:id="rId336" tooltip="https://www.amazon.frundefined"/>
+    <hyperlink ref="J47" r:id="rId337" tooltip="https://www.amazon.fr/dp/B075LJWKCY?psc=1"/>
+    <hyperlink ref="K47" r:id="rId338" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71LzhODZgmL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L47" r:id="rId339" tooltip="https://www.amazon.fr/dp/B075LJWKCY"/>
+    <hyperlink ref="C48" r:id="rId340" tooltip="https://www.amazon.fr/dp/B0FXX9KJ1D"/>
+    <hyperlink ref="G48" r:id="rId341" tooltip="https://www.amazon.frundefined"/>
+    <hyperlink ref="J48" r:id="rId342" tooltip="https://www.amazon.fr/dp/B0FXX9KJ1D?psc=1"/>
+    <hyperlink ref="K48" r:id="rId343" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51QsiPBPCjL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L48" r:id="rId344" tooltip="https://www.amazon.fr/dp/B0FXX9KJ1D"/>
+    <hyperlink ref="C49" r:id="rId345" tooltip="https://www.amazon.fr/dp/B0HFJJMHF6"/>
+    <hyperlink ref="G49" r:id="rId346" tooltip="https://www.amazon.frundefined"/>
+    <hyperlink ref="J49" r:id="rId347" tooltip="https://www.amazon.fr/dp/B0HFJJMHF6?psc=1"/>
+    <hyperlink ref="K49" r:id="rId348" tooltip="https://images-eu.ssl-images-amazon.com/images/I/41Q88WnGsRL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L49" r:id="rId349" tooltip="https://www.amazon.fr/dp/B0HFJJMHF6"/>
   </hyperlinks>
-  <drawing r:id="rId365"/>
+  <drawing r:id="rId350"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -19041,18 +18498,18 @@
         </is>
       </c>
       <c r="B2" s="15">
-        <v>13142</v>
+        <v>12813</v>
       </c>
       <c r="C2" s="15">
-        <v>901014</v>
+        <v>892792</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="20">
-        <v>68.55988434028306</v>
+        <v>69.67860766409116</v>
       </c>
       <c r="G2" s="22">
-        <v>0.6798055038278502</v>
+        <v>0.6747946071202865</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19073,7 +18530,7 @@
         <v>263.9191919191919</v>
       </c>
       <c r="G3" s="22">
-        <v>0.030726256983240222</v>
+        <v>0.03128291552559511</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19094,7 +18551,7 @@
         <v>136.58100558659217</v>
       </c>
       <c r="G4" s="22">
-        <v>0.046296296296296294</v>
+        <v>0.04713503265220139</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19115,7 +18572,7 @@
         <v>89.62628571428571</v>
       </c>
       <c r="G5" s="22">
-        <v>0.045261742189116494</v>
+        <v>0.046081735833157784</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19136,7 +18593,7 @@
         <v>64.00511508951406</v>
       </c>
       <c r="G6" s="22">
-        <v>0.06067659838609559</v>
+        <v>0.06177585843690752</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19157,7 +18614,7 @@
         <v>126.76106194690266</v>
       </c>
       <c r="G7" s="22">
-        <v>0.017535692116697702</v>
+        <v>0.01785338108278913</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19178,7 +18635,7 @@
         <v>99.90031152647975</v>
       </c>
       <c r="G8" s="22">
-        <v>0.016604593420235878</v>
+        <v>0.016905413945649886</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19199,7 +18656,7 @@
         <v>151.59375</v>
       </c>
       <c r="G9" s="22">
-        <v>0.008276432857438443</v>
+        <v>0.008426374552348851</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19220,7 +18677,7 @@
         <v>79.625</v>
       </c>
       <c r="G10" s="22">
-        <v>0.014069935857645354</v>
+        <v>0.014324836738993048</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19241,7 +18698,7 @@
         <v>63.320422535211264</v>
       </c>
       <c r="G11" s="22">
-        <v>0.014690668321953239</v>
+        <v>0.014956814830419211</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19262,7 +18719,7 @@
         <v>68.57916666666667</v>
       </c>
       <c r="G12" s="22">
-        <v>0.012414649286157667</v>
+        <v>0.012639561828523278</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19283,7 +18740,7 @@
         <v>128.2391304347826</v>
       </c>
       <c r="G13" s="22">
-        <v>0.004758948893027105</v>
+        <v>0.00484516536760059</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19304,7 +18761,7 @@
         <v>129.0</v>
       </c>
       <c r="G14" s="22">
-        <v>0.004086488723360232</v>
+        <v>0.004160522435222245</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19325,7 +18782,7 @@
         <v>79.99115044247787</v>
       </c>
       <c r="G15" s="22">
-        <v>0.005845230705565901</v>
+        <v>0.005951127027596377</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19346,7 +18803,7 @@
         <v>26.680851063829788</v>
       </c>
       <c r="G16" s="22">
-        <v>0.014587212911235258</v>
+        <v>0.01485148514851485</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19367,7 +18824,7 @@
         <v>75.35135135135135</v>
       </c>
       <c r="G17" s="22">
-        <v>0.0038278501965652804</v>
+        <v>0.003897198230461344</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19388,7 +18845,7 @@
         <v>28.398907103825138</v>
       </c>
       <c r="G18" s="22">
-        <v>0.00946617008069522</v>
+        <v>0.009637665894249</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19409,7 +18866,7 @@
         <v>65.54054054054055</v>
       </c>
       <c r="G19" s="22">
-        <v>0.0038278501965652804</v>
+        <v>0.003897198230461344</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19430,7 +18887,7 @@
         <v>68.56521739130434</v>
       </c>
       <c r="G20" s="22">
-        <v>0.003569211669770329</v>
+        <v>0.0036338740257004423</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19451,46 +18908,25 @@
         <v>63.892857142857146</v>
       </c>
       <c r="G21" s="22">
-        <v>0.0028967515001034555</v>
+        <v>0.002949231093322098</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>Vonia</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B22" s="15">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C22" s="15">
-        <v>937</v>
+        <v>0</v>
       </c>
       <c r="D22" s="15"/>
       <c r="E22" s="15"/>
-      <c r="F22" s="20">
-        <v>62.46666666666667</v>
-      </c>
+      <c r="F22" s="20"/>
       <c r="G22" s="22">
-        <v>0.0007759155803848542</v>
-      </c>
-    </row>
-    <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="B23" s="15">
-        <v>0</v>
-      </c>
-      <c r="C23" s="15">
-        <v>0</v>
-      </c>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="22">
         <v>0.0</v>
       </c>
     </row>
@@ -19502,7 +18938,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -19555,18 +18991,18 @@
         </is>
       </c>
       <c r="B2" s="15">
-        <v>16086</v>
+        <v>15757</v>
       </c>
       <c r="C2" s="15">
-        <v>1320723</v>
+        <v>1312501</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="20">
-        <v>82.10387914957106</v>
+        <v>83.29637621374627</v>
       </c>
       <c r="G2" s="22">
-        <v>0.8320918684047176</v>
+        <v>0.8298398988835054</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19587,7 +19023,7 @@
         <v>64.00511508951406</v>
       </c>
       <c r="G3" s="22">
-        <v>0.06067659838609559</v>
+        <v>0.06177585843690752</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19608,7 +19044,7 @@
         <v>99.90031152647975</v>
       </c>
       <c r="G4" s="22">
-        <v>0.016604593420235878</v>
+        <v>0.016905413945649886</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19629,7 +19065,7 @@
         <v>79.625</v>
       </c>
       <c r="G5" s="22">
-        <v>0.014069935857645354</v>
+        <v>0.014324836738993048</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19650,7 +19086,7 @@
         <v>151.9921875</v>
       </c>
       <c r="G6" s="22">
-        <v>0.006621146285950755</v>
+        <v>0.0067410996418790815</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19671,7 +19107,7 @@
         <v>68.57916666666667</v>
       </c>
       <c r="G7" s="22">
-        <v>0.012414649286157667</v>
+        <v>0.012639561828523278</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19692,7 +19128,7 @@
         <v>69.98979591836735</v>
       </c>
       <c r="G8" s="22">
-        <v>0.010138630250362093</v>
+        <v>0.010322308826627343</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19713,7 +19149,7 @@
         <v>128.2391304347826</v>
       </c>
       <c r="G9" s="22">
-        <v>0.004758948893027105</v>
+        <v>0.00484516536760059</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19734,7 +19170,7 @@
         <v>79.99115044247787</v>
       </c>
       <c r="G10" s="22">
-        <v>0.005845230705565901</v>
+        <v>0.005951127027596377</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19755,7 +19191,7 @@
         <v>26.680851063829788</v>
       </c>
       <c r="G11" s="22">
-        <v>0.014587212911235258</v>
+        <v>0.01485148514851485</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19776,7 +19212,7 @@
         <v>75.35135135135135</v>
       </c>
       <c r="G12" s="22">
-        <v>0.0038278501965652804</v>
+        <v>0.003897198230461344</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19797,7 +19233,7 @@
         <v>28.398907103825138</v>
       </c>
       <c r="G13" s="22">
-        <v>0.00946617008069522</v>
+        <v>0.009637665894249</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19818,7 +19254,7 @@
         <v>150.0</v>
       </c>
       <c r="G14" s="22">
-        <v>0.0016552865714876887</v>
+        <v>0.0016852749104697704</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19839,7 +19275,7 @@
         <v>68.56521739130434</v>
       </c>
       <c r="G15" s="22">
-        <v>0.003569211669770329</v>
+        <v>0.0036338740257004423</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19860,46 +19296,25 @@
         <v>63.892857142857146</v>
       </c>
       <c r="G16" s="22">
-        <v>0.0028967515001034555</v>
+        <v>0.002949231093322098</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>Dennepark B.V</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B17" s="15">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C17" s="15">
-        <v>937</v>
+        <v>0</v>
       </c>
       <c r="D17" s="15"/>
       <c r="E17" s="15"/>
-      <c r="F17" s="20">
-        <v>62.46666666666667</v>
-      </c>
+      <c r="F17" s="20"/>
       <c r="G17" s="22">
-        <v>0.0007759155803848542</v>
-      </c>
-    </row>
-    <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="B18" s="15">
-        <v>0</v>
-      </c>
-      <c r="C18" s="15">
-        <v>0</v>
-      </c>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="22">
         <v>0.0</v>
       </c>
     </row>
